--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210189</v>
+        <v>113210255</v>
       </c>
       <c r="B3" t="n">
-        <v>90029</v>
+        <v>78105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543860</v>
+        <v>543833</v>
       </c>
       <c r="R3" t="n">
-        <v>7204034</v>
+        <v>7204063</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210255</v>
+        <v>113210189</v>
       </c>
       <c r="B4" t="n">
-        <v>78105</v>
+        <v>90029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543833</v>
+        <v>543860</v>
       </c>
       <c r="R4" t="n">
-        <v>7204063</v>
+        <v>7204034</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210243</v>
+        <v>113210216</v>
       </c>
       <c r="B5" t="n">
-        <v>78105</v>
+        <v>79169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543980</v>
+        <v>543825</v>
       </c>
       <c r="R5" t="n">
-        <v>7204203</v>
+        <v>7204074</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210216</v>
+        <v>113210205</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79195</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543825</v>
+        <v>543834</v>
       </c>
       <c r="R6" t="n">
-        <v>7204074</v>
+        <v>7204061</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210205</v>
+        <v>113210243</v>
       </c>
       <c r="B7" t="n">
-        <v>79195</v>
+        <v>78105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543834</v>
+        <v>543980</v>
       </c>
       <c r="R7" t="n">
-        <v>7204061</v>
+        <v>7204203</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210184</v>
+        <v>113210254</v>
       </c>
       <c r="B9" t="n">
-        <v>77100</v>
+        <v>78105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543833</v>
+        <v>543828</v>
       </c>
       <c r="R9" t="n">
-        <v>7204064</v>
+        <v>7204074</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210254</v>
+        <v>113210184</v>
       </c>
       <c r="B10" t="n">
-        <v>78105</v>
+        <v>77100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543828</v>
+        <v>543833</v>
       </c>
       <c r="R10" t="n">
-        <v>7204074</v>
+        <v>7204064</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210215</v>
+        <v>113210252</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>78105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543762</v>
+        <v>543761</v>
       </c>
       <c r="R12" t="n">
-        <v>7204149</v>
+        <v>7204153</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210252</v>
+        <v>113210215</v>
       </c>
       <c r="B13" t="n">
-        <v>78105</v>
+        <v>79169</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543761</v>
+        <v>543762</v>
       </c>
       <c r="R13" t="n">
-        <v>7204153</v>
+        <v>7204149</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210208</v>
+        <v>113210224</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>74307</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543983</v>
+        <v>543833</v>
       </c>
       <c r="R2" t="n">
-        <v>7204228</v>
+        <v>7204069</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210255</v>
+        <v>113210204</v>
       </c>
       <c r="B3" t="n">
-        <v>78105</v>
+        <v>57362</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543833</v>
+        <v>543834</v>
       </c>
       <c r="R3" t="n">
-        <v>7204063</v>
+        <v>7204061</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210189</v>
+        <v>113210252</v>
       </c>
       <c r="B4" t="n">
-        <v>90029</v>
+        <v>78121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543860</v>
+        <v>543761</v>
       </c>
       <c r="R4" t="n">
-        <v>7204034</v>
+        <v>7204153</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210216</v>
+        <v>113210215</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543825</v>
+        <v>543762</v>
       </c>
       <c r="R5" t="n">
-        <v>7204074</v>
+        <v>7204149</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210205</v>
+        <v>113210189</v>
       </c>
       <c r="B6" t="n">
-        <v>79195</v>
+        <v>90045</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1144,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543834</v>
+        <v>543860</v>
       </c>
       <c r="R6" t="n">
-        <v>7204061</v>
+        <v>7204034</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210243</v>
+        <v>113210279</v>
       </c>
       <c r="B7" t="n">
-        <v>78105</v>
+        <v>81862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543980</v>
+        <v>543833</v>
       </c>
       <c r="R7" t="n">
-        <v>7204203</v>
+        <v>7204061</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210240</v>
+        <v>113210280</v>
       </c>
       <c r="B8" t="n">
-        <v>78105</v>
+        <v>86341</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544111</v>
+        <v>543753</v>
       </c>
       <c r="R8" t="n">
-        <v>7204146</v>
+        <v>7204132</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210254</v>
+        <v>113210202</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>56910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,34 +1484,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543828</v>
+        <v>544006</v>
       </c>
       <c r="R9" t="n">
-        <v>7204074</v>
+        <v>7204169</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210184</v>
+        <v>113210208</v>
       </c>
       <c r="B10" t="n">
-        <v>77100</v>
+        <v>79185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543833</v>
+        <v>543983</v>
       </c>
       <c r="R10" t="n">
-        <v>7204064</v>
+        <v>7204228</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210245</v>
+        <v>113210212</v>
       </c>
       <c r="B11" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544004</v>
+        <v>543892</v>
       </c>
       <c r="R11" t="n">
-        <v>7204167</v>
+        <v>7204108</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210252</v>
+        <v>113210211</v>
       </c>
       <c r="B12" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1824,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543761</v>
+        <v>544004</v>
       </c>
       <c r="R12" t="n">
-        <v>7204153</v>
+        <v>7204168</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210215</v>
+        <v>113210256</v>
       </c>
       <c r="B13" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543762</v>
+        <v>543835</v>
       </c>
       <c r="R13" t="n">
-        <v>7204149</v>
+        <v>7204062</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210202</v>
+        <v>113210249</v>
       </c>
       <c r="B14" t="n">
-        <v>56910</v>
+        <v>78121</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,38 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544006</v>
+        <v>543857</v>
       </c>
       <c r="R14" t="n">
-        <v>7204169</v>
+        <v>7204152</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210257</v>
+        <v>113210209</v>
       </c>
       <c r="B15" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,21 +2160,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543860</v>
+        <v>543983</v>
       </c>
       <c r="R15" t="n">
-        <v>7204033</v>
+        <v>7204203</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210236</v>
+        <v>113210227</v>
       </c>
       <c r="B16" t="n">
-        <v>78186</v>
+        <v>79184</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,21 +2272,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544118</v>
+        <v>543983</v>
       </c>
       <c r="R16" t="n">
-        <v>7204143</v>
+        <v>7204228</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210248</v>
+        <v>113210231</v>
       </c>
       <c r="B17" t="n">
-        <v>78105</v>
+        <v>79218</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,25 +2380,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543892</v>
+        <v>543836</v>
       </c>
       <c r="R17" t="n">
-        <v>7204111</v>
+        <v>7204058</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210210</v>
+        <v>113210214</v>
       </c>
       <c r="B18" t="n">
-        <v>79169</v>
+        <v>79185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543984</v>
+        <v>543810</v>
       </c>
       <c r="R18" t="n">
-        <v>7204167</v>
+        <v>7204198</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210207</v>
+        <v>113210235</v>
       </c>
       <c r="B19" t="n">
-        <v>79169</v>
+        <v>77478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,25 +2604,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544012</v>
+        <v>543858</v>
       </c>
       <c r="R19" t="n">
-        <v>7204204</v>
+        <v>7204151</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210256</v>
+        <v>113210253</v>
       </c>
       <c r="B20" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543835</v>
+        <v>543753</v>
       </c>
       <c r="R20" t="n">
-        <v>7204062</v>
+        <v>7204127</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210235</v>
+        <v>113210242</v>
       </c>
       <c r="B21" t="n">
-        <v>77462</v>
+        <v>78121</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,25 +2828,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543858</v>
+        <v>543981</v>
       </c>
       <c r="R21" t="n">
-        <v>7204151</v>
+        <v>7204228</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210224</v>
+        <v>113210255</v>
       </c>
       <c r="B22" t="n">
-        <v>74291</v>
+        <v>78121</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,21 +2944,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2962,7 +2971,7 @@
         <v>543833</v>
       </c>
       <c r="R22" t="n">
-        <v>7204069</v>
+        <v>7204063</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210214</v>
+        <v>113210246</v>
       </c>
       <c r="B23" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543810</v>
+        <v>543953</v>
       </c>
       <c r="R23" t="n">
-        <v>7204198</v>
+        <v>7204079</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3106,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210244</v>
+        <v>113210257</v>
       </c>
       <c r="B24" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3183,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543984</v>
+        <v>543860</v>
       </c>
       <c r="R24" t="n">
-        <v>7204170</v>
+        <v>7204033</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3218,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210185</v>
+        <v>113210210</v>
       </c>
       <c r="B25" t="n">
-        <v>74286</v>
+        <v>79185</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3271,21 +3280,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543833</v>
+        <v>543984</v>
       </c>
       <c r="R25" t="n">
-        <v>7204064</v>
+        <v>7204167</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3330,7 +3339,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3340,7 +3349,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,10 +3376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210280</v>
+        <v>113210205</v>
       </c>
       <c r="B26" t="n">
-        <v>86325</v>
+        <v>79211</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,25 +3388,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3407,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543753</v>
+        <v>543834</v>
       </c>
       <c r="R26" t="n">
-        <v>7204132</v>
+        <v>7204061</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3442,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3452,7 +3461,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210250</v>
+        <v>113210216</v>
       </c>
       <c r="B27" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3495,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3519,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543822</v>
+        <v>543825</v>
       </c>
       <c r="R27" t="n">
-        <v>7204196</v>
+        <v>7204074</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3554,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3564,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210217</v>
+        <v>113210191</v>
       </c>
       <c r="B28" t="n">
-        <v>79169</v>
+        <v>56765</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,34 +3616,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543841</v>
+        <v>543999</v>
       </c>
       <c r="R28" t="n">
-        <v>7204061</v>
+        <v>7204066</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3666,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3676,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210226</v>
+        <v>113210185</v>
       </c>
       <c r="B29" t="n">
-        <v>79168</v>
+        <v>74302</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,21 +3737,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3743,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544013</v>
+        <v>543833</v>
       </c>
       <c r="R29" t="n">
-        <v>7204205</v>
+        <v>7204064</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3778,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3788,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,10 +3833,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210233</v>
+        <v>113210250</v>
       </c>
       <c r="B30" t="n">
-        <v>77086</v>
+        <v>78121</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3831,21 +3849,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3855,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543835</v>
+        <v>543822</v>
       </c>
       <c r="R30" t="n">
-        <v>7204068</v>
+        <v>7204196</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3890,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3900,7 +3918,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210211</v>
+        <v>113210243</v>
       </c>
       <c r="B31" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3943,21 +3961,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3967,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544004</v>
+        <v>543980</v>
       </c>
       <c r="R31" t="n">
-        <v>7204168</v>
+        <v>7204203</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4002,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4012,7 +4030,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,10 +4057,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210251</v>
+        <v>113210236</v>
       </c>
       <c r="B32" t="n">
-        <v>78105</v>
+        <v>78202</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4055,21 +4073,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4079,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543809</v>
+        <v>544118</v>
       </c>
       <c r="R32" t="n">
-        <v>7204195</v>
+        <v>7204143</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4114,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4124,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4151,10 +4169,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210231</v>
+        <v>113210233</v>
       </c>
       <c r="B33" t="n">
-        <v>79202</v>
+        <v>77102</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,25 +4181,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4191,10 +4209,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543836</v>
+        <v>543835</v>
       </c>
       <c r="R33" t="n">
-        <v>7204058</v>
+        <v>7204068</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4226,7 +4244,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4236,7 +4254,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210228</v>
+        <v>113210217</v>
       </c>
       <c r="B34" t="n">
-        <v>79168</v>
+        <v>79185</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4279,21 +4297,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4303,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544004</v>
+        <v>543841</v>
       </c>
       <c r="R34" t="n">
-        <v>7204167</v>
+        <v>7204061</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4338,7 +4356,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4348,7 +4366,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,10 +4393,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210191</v>
+        <v>113210251</v>
       </c>
       <c r="B35" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,43 +4409,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543999</v>
+        <v>543809</v>
       </c>
       <c r="R35" t="n">
-        <v>7204066</v>
+        <v>7204195</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4459,7 +4468,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4469,7 +4478,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4499,7 +4508,7 @@
         <v>113210281</v>
       </c>
       <c r="B36" t="n">
-        <v>79201</v>
+        <v>79217</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4608,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210249</v>
+        <v>113210278</v>
       </c>
       <c r="B37" t="n">
-        <v>78105</v>
+        <v>81862</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4624,21 +4633,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4657,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543857</v>
+        <v>543835</v>
       </c>
       <c r="R37" t="n">
-        <v>7204152</v>
+        <v>7204068</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4683,7 +4692,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4693,7 +4702,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4729,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210213</v>
+        <v>113210240</v>
       </c>
       <c r="B38" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,21 +4745,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4760,10 +4769,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543821</v>
+        <v>544111</v>
       </c>
       <c r="R38" t="n">
-        <v>7204193</v>
+        <v>7204146</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4795,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4814,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4832,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210246</v>
+        <v>113210207</v>
       </c>
       <c r="B39" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4848,21 +4857,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4872,10 +4881,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543953</v>
+        <v>544012</v>
       </c>
       <c r="R39" t="n">
-        <v>7204079</v>
+        <v>7204204</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4907,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4917,7 +4926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,10 +4953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210209</v>
+        <v>113210241</v>
       </c>
       <c r="B40" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4960,21 +4969,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4984,10 +4993,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543983</v>
+        <v>544013</v>
       </c>
       <c r="R40" t="n">
-        <v>7204203</v>
+        <v>7204204</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5019,7 +5028,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5029,7 +5038,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5056,10 +5065,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210279</v>
+        <v>113210245</v>
       </c>
       <c r="B41" t="n">
-        <v>81846</v>
+        <v>78121</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5072,21 +5081,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5096,10 +5105,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543833</v>
+        <v>544004</v>
       </c>
       <c r="R41" t="n">
-        <v>7204061</v>
+        <v>7204167</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5131,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5141,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,10 +5177,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210253</v>
+        <v>113210213</v>
       </c>
       <c r="B42" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5184,21 +5193,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5208,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543753</v>
+        <v>543821</v>
       </c>
       <c r="R42" t="n">
-        <v>7204127</v>
+        <v>7204193</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5243,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5253,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5283,7 +5292,7 @@
         <v>113210238</v>
       </c>
       <c r="B43" t="n">
-        <v>90047</v>
+        <v>90063</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5392,10 +5401,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210242</v>
+        <v>113210248</v>
       </c>
       <c r="B44" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,10 +5441,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543981</v>
+        <v>543892</v>
       </c>
       <c r="R44" t="n">
-        <v>7204228</v>
+        <v>7204111</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5467,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5477,7 +5486,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5504,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210204</v>
+        <v>113210254</v>
       </c>
       <c r="B45" t="n">
-        <v>57362</v>
+        <v>78121</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5516,47 +5525,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543834</v>
+        <v>543828</v>
       </c>
       <c r="R45" t="n">
-        <v>7204061</v>
+        <v>7204074</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210230</v>
+        <v>113210226</v>
       </c>
       <c r="B46" t="n">
-        <v>79202</v>
+        <v>79184</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5637,25 +5637,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543826</v>
+        <v>544013</v>
       </c>
       <c r="R46" t="n">
-        <v>7204074</v>
+        <v>7204205</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210212</v>
+        <v>113210230</v>
       </c>
       <c r="B47" t="n">
-        <v>79169</v>
+        <v>79218</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543892</v>
+        <v>543826</v>
       </c>
       <c r="R47" t="n">
-        <v>7204108</v>
+        <v>7204074</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210227</v>
+        <v>113210228</v>
       </c>
       <c r="B48" t="n">
-        <v>79168</v>
+        <v>79184</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543983</v>
+        <v>544004</v>
       </c>
       <c r="R48" t="n">
-        <v>7204228</v>
+        <v>7204167</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210241</v>
+        <v>113210184</v>
       </c>
       <c r="B49" t="n">
-        <v>78105</v>
+        <v>77116</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544013</v>
+        <v>543833</v>
       </c>
       <c r="R49" t="n">
-        <v>7204204</v>
+        <v>7204064</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210278</v>
+        <v>113210244</v>
       </c>
       <c r="B50" t="n">
-        <v>81846</v>
+        <v>78121</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543835</v>
+        <v>543984</v>
       </c>
       <c r="R50" t="n">
-        <v>7204068</v>
+        <v>7204170</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210224</v>
+        <v>113210252</v>
       </c>
       <c r="B2" t="n">
-        <v>74307</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543833</v>
+        <v>543761</v>
       </c>
       <c r="R2" t="n">
-        <v>7204069</v>
+        <v>7204153</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210204</v>
+        <v>113210215</v>
       </c>
       <c r="B3" t="n">
-        <v>57362</v>
+        <v>79185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543834</v>
+        <v>543762</v>
       </c>
       <c r="R3" t="n">
-        <v>7204061</v>
+        <v>7204149</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210252</v>
+        <v>113210224</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>74307</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543761</v>
+        <v>543833</v>
       </c>
       <c r="R4" t="n">
-        <v>7204153</v>
+        <v>7204069</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210215</v>
+        <v>113210204</v>
       </c>
       <c r="B5" t="n">
-        <v>79185</v>
+        <v>57362</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543762</v>
+        <v>543834</v>
       </c>
       <c r="R5" t="n">
-        <v>7204149</v>
+        <v>7204061</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3376,10 +3376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210205</v>
+        <v>113210185</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>74302</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3388,25 +3388,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543834</v>
+        <v>543833</v>
       </c>
       <c r="R26" t="n">
-        <v>7204061</v>
+        <v>7204064</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210216</v>
+        <v>113210250</v>
       </c>
       <c r="B27" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543825</v>
+        <v>543822</v>
       </c>
       <c r="R27" t="n">
-        <v>7204074</v>
+        <v>7204196</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210191</v>
+        <v>113210243</v>
       </c>
       <c r="B28" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,43 +3616,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543999</v>
+        <v>543980</v>
       </c>
       <c r="R28" t="n">
-        <v>7204066</v>
+        <v>7204203</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3684,7 +3675,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3685,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3712,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210185</v>
+        <v>113210205</v>
       </c>
       <c r="B29" t="n">
-        <v>74302</v>
+        <v>79211</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,25 +3724,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543833</v>
+        <v>543834</v>
       </c>
       <c r="R29" t="n">
-        <v>7204064</v>
+        <v>7204061</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3796,7 +3787,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3797,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,10 +3824,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210250</v>
+        <v>113210236</v>
       </c>
       <c r="B30" t="n">
-        <v>78121</v>
+        <v>78202</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3849,21 +3840,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3873,10 +3864,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543822</v>
+        <v>544118</v>
       </c>
       <c r="R30" t="n">
-        <v>7204196</v>
+        <v>7204143</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3908,7 +3899,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,7 +3909,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,10 +3936,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210243</v>
+        <v>113210191</v>
       </c>
       <c r="B31" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3961,34 +3952,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543980</v>
+        <v>543999</v>
       </c>
       <c r="R31" t="n">
-        <v>7204203</v>
+        <v>7204066</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,10 +4057,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210236</v>
+        <v>113210216</v>
       </c>
       <c r="B32" t="n">
-        <v>78202</v>
+        <v>79185</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544118</v>
+        <v>543825</v>
       </c>
       <c r="R32" t="n">
-        <v>7204143</v>
+        <v>7204074</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4953,10 +4953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210241</v>
+        <v>113210213</v>
       </c>
       <c r="B40" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544013</v>
+        <v>543821</v>
       </c>
       <c r="R40" t="n">
-        <v>7204204</v>
+        <v>7204193</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5065,7 +5065,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210245</v>
+        <v>113210241</v>
       </c>
       <c r="B41" t="n">
         <v>78121</v>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544004</v>
+        <v>544013</v>
       </c>
       <c r="R41" t="n">
-        <v>7204167</v>
+        <v>7204204</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210213</v>
+        <v>113210245</v>
       </c>
       <c r="B42" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5193,21 +5193,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543821</v>
+        <v>544004</v>
       </c>
       <c r="R42" t="n">
-        <v>7204193</v>
+        <v>7204167</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5849,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210228</v>
+        <v>113210184</v>
       </c>
       <c r="B48" t="n">
-        <v>79184</v>
+        <v>77116</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544004</v>
+        <v>543833</v>
       </c>
       <c r="R48" t="n">
-        <v>7204167</v>
+        <v>7204064</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210184</v>
+        <v>113210244</v>
       </c>
       <c r="B49" t="n">
-        <v>77116</v>
+        <v>78121</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543833</v>
+        <v>543984</v>
       </c>
       <c r="R49" t="n">
-        <v>7204064</v>
+        <v>7204170</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210244</v>
+        <v>113210228</v>
       </c>
       <c r="B50" t="n">
-        <v>78121</v>
+        <v>79184</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543984</v>
+        <v>544004</v>
       </c>
       <c r="R50" t="n">
-        <v>7204170</v>
+        <v>7204167</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210252</v>
+        <v>113210238</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543761</v>
+        <v>543860</v>
       </c>
       <c r="R2" t="n">
-        <v>7204153</v>
+        <v>7204033</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210215</v>
+        <v>113210253</v>
       </c>
       <c r="B3" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543762</v>
+        <v>543753</v>
       </c>
       <c r="R3" t="n">
-        <v>7204149</v>
+        <v>7204127</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210224</v>
+        <v>113210256</v>
       </c>
       <c r="B4" t="n">
-        <v>74307</v>
+        <v>78121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543833</v>
+        <v>543835</v>
       </c>
       <c r="R4" t="n">
-        <v>7204069</v>
+        <v>7204062</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210204</v>
+        <v>113210280</v>
       </c>
       <c r="B5" t="n">
-        <v>57362</v>
+        <v>86341</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102125</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543834</v>
+        <v>543753</v>
       </c>
       <c r="R5" t="n">
-        <v>7204061</v>
+        <v>7204132</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210189</v>
+        <v>113210235</v>
       </c>
       <c r="B6" t="n">
-        <v>90045</v>
+        <v>77478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543860</v>
+        <v>543858</v>
       </c>
       <c r="R6" t="n">
-        <v>7204034</v>
+        <v>7204151</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210279</v>
+        <v>113210278</v>
       </c>
       <c r="B7" t="n">
         <v>81862</v>
@@ -1284,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543833</v>
+        <v>543835</v>
       </c>
       <c r="R7" t="n">
-        <v>7204061</v>
+        <v>7204068</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210280</v>
+        <v>113210250</v>
       </c>
       <c r="B8" t="n">
-        <v>86341</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543753</v>
+        <v>543822</v>
       </c>
       <c r="R8" t="n">
-        <v>7204132</v>
+        <v>7204196</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210202</v>
+        <v>113210242</v>
       </c>
       <c r="B9" t="n">
-        <v>56910</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,38 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544006</v>
+        <v>543981</v>
       </c>
       <c r="R9" t="n">
-        <v>7204169</v>
+        <v>7204228</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1547,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210208</v>
+        <v>113210248</v>
       </c>
       <c r="B10" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543983</v>
+        <v>543892</v>
       </c>
       <c r="R10" t="n">
-        <v>7204228</v>
+        <v>7204111</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210212</v>
+        <v>113210236</v>
       </c>
       <c r="B11" t="n">
-        <v>79185</v>
+        <v>78202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543892</v>
+        <v>544118</v>
       </c>
       <c r="R11" t="n">
-        <v>7204108</v>
+        <v>7204143</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1771,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210211</v>
+        <v>113210212</v>
       </c>
       <c r="B12" t="n">
         <v>79185</v>
@@ -1848,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544004</v>
+        <v>543892</v>
       </c>
       <c r="R12" t="n">
-        <v>7204168</v>
+        <v>7204108</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1883,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210256</v>
+        <v>113210216</v>
       </c>
       <c r="B13" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543835</v>
+        <v>543825</v>
       </c>
       <c r="R13" t="n">
-        <v>7204062</v>
+        <v>7204074</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1995,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210249</v>
+        <v>113210217</v>
       </c>
       <c r="B14" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543857</v>
+        <v>543841</v>
       </c>
       <c r="R14" t="n">
-        <v>7204152</v>
+        <v>7204061</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210209</v>
+        <v>113210241</v>
       </c>
       <c r="B15" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2184,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543983</v>
+        <v>544013</v>
       </c>
       <c r="R15" t="n">
-        <v>7204203</v>
+        <v>7204204</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2219,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210227</v>
+        <v>113210254</v>
       </c>
       <c r="B16" t="n">
-        <v>79184</v>
+        <v>78121</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543983</v>
+        <v>543828</v>
       </c>
       <c r="R16" t="n">
-        <v>7204228</v>
+        <v>7204074</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210231</v>
+        <v>113210249</v>
       </c>
       <c r="B17" t="n">
-        <v>79218</v>
+        <v>78121</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543836</v>
+        <v>543857</v>
       </c>
       <c r="R17" t="n">
-        <v>7204058</v>
+        <v>7204152</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2467,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210214</v>
+        <v>113210210</v>
       </c>
       <c r="B18" t="n">
         <v>79185</v>
@@ -2520,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543810</v>
+        <v>543984</v>
       </c>
       <c r="R18" t="n">
-        <v>7204198</v>
+        <v>7204167</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2555,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210235</v>
+        <v>113210227</v>
       </c>
       <c r="B19" t="n">
-        <v>77478</v>
+        <v>79184</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>498</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543858</v>
+        <v>543983</v>
       </c>
       <c r="R19" t="n">
-        <v>7204151</v>
+        <v>7204228</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2667,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210253</v>
+        <v>113210214</v>
       </c>
       <c r="B20" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543753</v>
+        <v>543810</v>
       </c>
       <c r="R20" t="n">
-        <v>7204127</v>
+        <v>7204198</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2779,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210242</v>
+        <v>113210257</v>
       </c>
       <c r="B21" t="n">
         <v>78121</v>
@@ -2856,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543981</v>
+        <v>543860</v>
       </c>
       <c r="R21" t="n">
-        <v>7204228</v>
+        <v>7204033</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3040,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210246</v>
+        <v>113210233</v>
       </c>
       <c r="B23" t="n">
-        <v>78121</v>
+        <v>77102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543953</v>
+        <v>543835</v>
       </c>
       <c r="R23" t="n">
-        <v>7204079</v>
+        <v>7204068</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3115,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210257</v>
+        <v>113210226</v>
       </c>
       <c r="B24" t="n">
-        <v>78121</v>
+        <v>79184</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543860</v>
+        <v>544013</v>
       </c>
       <c r="R24" t="n">
-        <v>7204033</v>
+        <v>7204205</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210210</v>
+        <v>113210185</v>
       </c>
       <c r="B25" t="n">
-        <v>79185</v>
+        <v>74302</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3280,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543984</v>
+        <v>543833</v>
       </c>
       <c r="R25" t="n">
-        <v>7204167</v>
+        <v>7204064</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3339,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3349,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210185</v>
+        <v>113210230</v>
       </c>
       <c r="B26" t="n">
-        <v>74302</v>
+        <v>79218</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3388,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3416,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543833</v>
+        <v>543826</v>
       </c>
       <c r="R26" t="n">
-        <v>7204064</v>
+        <v>7204074</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3451,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3488,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210250</v>
+        <v>113210281</v>
       </c>
       <c r="B27" t="n">
-        <v>78121</v>
+        <v>79217</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,20 +3487,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3528,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543822</v>
+        <v>543834</v>
       </c>
       <c r="R27" t="n">
-        <v>7204196</v>
+        <v>7204070</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3563,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,7 +3587,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210243</v>
+        <v>113210252</v>
       </c>
       <c r="B28" t="n">
         <v>78121</v>
@@ -3640,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543980</v>
+        <v>543761</v>
       </c>
       <c r="R28" t="n">
-        <v>7204203</v>
+        <v>7204153</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3675,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3685,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3824,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210236</v>
+        <v>113210202</v>
       </c>
       <c r="B30" t="n">
-        <v>78202</v>
+        <v>56910</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3840,34 +3827,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544118</v>
+        <v>544006</v>
       </c>
       <c r="R30" t="n">
-        <v>7204143</v>
+        <v>7204169</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3899,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3909,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3936,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210191</v>
+        <v>113210244</v>
       </c>
       <c r="B31" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3952,43 +3943,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543999</v>
+        <v>543984</v>
       </c>
       <c r="R31" t="n">
-        <v>7204066</v>
+        <v>7204170</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4020,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210216</v>
+        <v>113210231</v>
       </c>
       <c r="B32" t="n">
-        <v>79185</v>
+        <v>79218</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4069,25 +4051,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4097,10 +4079,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543825</v>
+        <v>543836</v>
       </c>
       <c r="R32" t="n">
-        <v>7204074</v>
+        <v>7204058</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4132,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4142,7 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210233</v>
+        <v>113210204</v>
       </c>
       <c r="B33" t="n">
-        <v>77102</v>
+        <v>57362</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,38 +4163,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>102125</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543835</v>
+        <v>543834</v>
       </c>
       <c r="R33" t="n">
-        <v>7204068</v>
+        <v>7204061</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4244,7 +4235,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4254,7 +4245,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210217</v>
+        <v>113210245</v>
       </c>
       <c r="B34" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4297,21 +4288,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543841</v>
+        <v>544004</v>
       </c>
       <c r="R34" t="n">
-        <v>7204061</v>
+        <v>7204167</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4356,7 +4347,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4366,7 +4357,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,10 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210251</v>
+        <v>113210279</v>
       </c>
       <c r="B35" t="n">
-        <v>78121</v>
+        <v>81862</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4409,21 +4400,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4433,10 +4424,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543809</v>
+        <v>543833</v>
       </c>
       <c r="R35" t="n">
-        <v>7204195</v>
+        <v>7204061</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4468,7 +4459,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,7 +4469,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4505,10 +4496,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210281</v>
+        <v>113210215</v>
       </c>
       <c r="B36" t="n">
-        <v>79217</v>
+        <v>79185</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4517,25 +4508,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4545,10 +4536,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543834</v>
+        <v>543762</v>
       </c>
       <c r="R36" t="n">
-        <v>7204070</v>
+        <v>7204149</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4580,7 +4571,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4590,7 +4581,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210278</v>
+        <v>113210189</v>
       </c>
       <c r="B37" t="n">
-        <v>81862</v>
+        <v>90045</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4633,21 +4624,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4657,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543835</v>
+        <v>543860</v>
       </c>
       <c r="R37" t="n">
-        <v>7204068</v>
+        <v>7204034</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4692,7 +4683,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4702,7 +4693,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,7 +4720,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210240</v>
+        <v>113210243</v>
       </c>
       <c r="B38" t="n">
         <v>78121</v>
@@ -4769,10 +4760,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544111</v>
+        <v>543980</v>
       </c>
       <c r="R38" t="n">
-        <v>7204146</v>
+        <v>7204203</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4804,7 +4795,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,7 +4805,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4832,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210207</v>
+        <v>113210251</v>
       </c>
       <c r="B39" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4857,21 +4848,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4881,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544012</v>
+        <v>543809</v>
       </c>
       <c r="R39" t="n">
-        <v>7204204</v>
+        <v>7204195</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4916,7 +4907,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4926,7 +4917,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5065,10 +5056,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210241</v>
+        <v>113210208</v>
       </c>
       <c r="B41" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5081,21 +5072,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5105,10 +5096,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544013</v>
+        <v>543983</v>
       </c>
       <c r="R41" t="n">
-        <v>7204204</v>
+        <v>7204228</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5140,7 +5131,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5150,7 +5141,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5177,10 +5168,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210245</v>
+        <v>113210207</v>
       </c>
       <c r="B42" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5193,21 +5184,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5217,10 +5208,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544004</v>
+        <v>544012</v>
       </c>
       <c r="R42" t="n">
-        <v>7204167</v>
+        <v>7204204</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5252,7 +5243,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5253,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5289,10 +5280,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210238</v>
+        <v>113210184</v>
       </c>
       <c r="B43" t="n">
-        <v>90063</v>
+        <v>77116</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5305,21 +5296,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5329,10 +5320,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543860</v>
+        <v>543833</v>
       </c>
       <c r="R43" t="n">
-        <v>7204033</v>
+        <v>7204064</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5364,7 +5355,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5374,7 +5365,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5401,7 +5392,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210248</v>
+        <v>113210246</v>
       </c>
       <c r="B44" t="n">
         <v>78121</v>
@@ -5441,10 +5432,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543892</v>
+        <v>543953</v>
       </c>
       <c r="R44" t="n">
-        <v>7204111</v>
+        <v>7204079</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5476,7 +5467,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5486,7 +5477,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5513,10 +5504,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210254</v>
+        <v>113210228</v>
       </c>
       <c r="B45" t="n">
-        <v>78121</v>
+        <v>79184</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5529,21 +5520,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5553,10 +5544,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543828</v>
+        <v>544004</v>
       </c>
       <c r="R45" t="n">
-        <v>7204074</v>
+        <v>7204167</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5588,7 +5579,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5598,7 +5589,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5625,10 +5616,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210226</v>
+        <v>113210224</v>
       </c>
       <c r="B46" t="n">
-        <v>79184</v>
+        <v>74307</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5641,21 +5632,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5665,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544013</v>
+        <v>543833</v>
       </c>
       <c r="R46" t="n">
-        <v>7204205</v>
+        <v>7204069</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5691,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5701,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210230</v>
+        <v>113210240</v>
       </c>
       <c r="B47" t="n">
-        <v>79218</v>
+        <v>78121</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5740,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5768,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543826</v>
+        <v>544111</v>
       </c>
       <c r="R47" t="n">
-        <v>7204074</v>
+        <v>7204146</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5803,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5813,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5840,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210184</v>
+        <v>113210191</v>
       </c>
       <c r="B48" t="n">
-        <v>77116</v>
+        <v>56765</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5865,34 +5856,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543833</v>
+        <v>543999</v>
       </c>
       <c r="R48" t="n">
-        <v>7204064</v>
+        <v>7204066</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210244</v>
+        <v>113210211</v>
       </c>
       <c r="B49" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543984</v>
+        <v>544004</v>
       </c>
       <c r="R49" t="n">
-        <v>7204170</v>
+        <v>7204168</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210228</v>
+        <v>113210209</v>
       </c>
       <c r="B50" t="n">
-        <v>79184</v>
+        <v>79185</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544004</v>
+        <v>543983</v>
       </c>
       <c r="R50" t="n">
-        <v>7204167</v>
+        <v>7204203</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210238</v>
+        <v>113210227</v>
       </c>
       <c r="B2" t="n">
-        <v>90063</v>
+        <v>79196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543860</v>
+        <v>543983</v>
       </c>
       <c r="R2" t="n">
-        <v>7204033</v>
+        <v>7204228</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210253</v>
+        <v>113210185</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>74314</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543753</v>
+        <v>543833</v>
       </c>
       <c r="R3" t="n">
-        <v>7204127</v>
+        <v>7204064</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210256</v>
+        <v>113210253</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543835</v>
+        <v>543753</v>
       </c>
       <c r="R4" t="n">
-        <v>7204062</v>
+        <v>7204127</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210280</v>
+        <v>113210281</v>
       </c>
       <c r="B5" t="n">
-        <v>86341</v>
+        <v>79229</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543753</v>
+        <v>543834</v>
       </c>
       <c r="R5" t="n">
-        <v>7204132</v>
+        <v>7204070</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210235</v>
+        <v>113210233</v>
       </c>
       <c r="B6" t="n">
-        <v>77478</v>
+        <v>77114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>498</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543858</v>
+        <v>543835</v>
       </c>
       <c r="R6" t="n">
-        <v>7204151</v>
+        <v>7204068</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210278</v>
+        <v>113210279</v>
       </c>
       <c r="B7" t="n">
-        <v>81862</v>
+        <v>81874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543835</v>
+        <v>543833</v>
       </c>
       <c r="R7" t="n">
-        <v>7204068</v>
+        <v>7204061</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210250</v>
+        <v>113210236</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>78214</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543822</v>
+        <v>544118</v>
       </c>
       <c r="R8" t="n">
-        <v>7204196</v>
+        <v>7204143</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210242</v>
+        <v>113210184</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>77128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543981</v>
+        <v>543833</v>
       </c>
       <c r="R9" t="n">
-        <v>7204228</v>
+        <v>7204064</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210248</v>
+        <v>113210189</v>
       </c>
       <c r="B10" t="n">
-        <v>78121</v>
+        <v>90057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543892</v>
+        <v>543860</v>
       </c>
       <c r="R10" t="n">
-        <v>7204111</v>
+        <v>7204034</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210236</v>
+        <v>113210246</v>
       </c>
       <c r="B11" t="n">
-        <v>78202</v>
+        <v>78133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544118</v>
+        <v>543953</v>
       </c>
       <c r="R11" t="n">
-        <v>7204143</v>
+        <v>7204079</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210212</v>
+        <v>113210216</v>
       </c>
       <c r="B12" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543892</v>
+        <v>543825</v>
       </c>
       <c r="R12" t="n">
-        <v>7204108</v>
+        <v>7204074</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210216</v>
+        <v>113210214</v>
       </c>
       <c r="B13" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543825</v>
+        <v>543810</v>
       </c>
       <c r="R13" t="n">
-        <v>7204074</v>
+        <v>7204198</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210217</v>
+        <v>113210250</v>
       </c>
       <c r="B14" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543841</v>
+        <v>543822</v>
       </c>
       <c r="R14" t="n">
-        <v>7204061</v>
+        <v>7204196</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210241</v>
+        <v>113210249</v>
       </c>
       <c r="B15" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544013</v>
+        <v>543857</v>
       </c>
       <c r="R15" t="n">
-        <v>7204204</v>
+        <v>7204152</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210254</v>
+        <v>113210256</v>
       </c>
       <c r="B16" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543828</v>
+        <v>543835</v>
       </c>
       <c r="R16" t="n">
-        <v>7204074</v>
+        <v>7204062</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210249</v>
+        <v>113210212</v>
       </c>
       <c r="B17" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543857</v>
+        <v>543892</v>
       </c>
       <c r="R17" t="n">
-        <v>7204152</v>
+        <v>7204108</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210210</v>
+        <v>113210215</v>
       </c>
       <c r="B18" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543984</v>
+        <v>543762</v>
       </c>
       <c r="R18" t="n">
-        <v>7204167</v>
+        <v>7204149</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210227</v>
+        <v>113210238</v>
       </c>
       <c r="B19" t="n">
-        <v>79184</v>
+        <v>90075</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543983</v>
+        <v>543860</v>
       </c>
       <c r="R19" t="n">
-        <v>7204228</v>
+        <v>7204033</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210214</v>
+        <v>113210209</v>
       </c>
       <c r="B20" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543810</v>
+        <v>543983</v>
       </c>
       <c r="R20" t="n">
-        <v>7204198</v>
+        <v>7204203</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210257</v>
+        <v>113210191</v>
       </c>
       <c r="B21" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,34 +2819,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543860</v>
+        <v>543999</v>
       </c>
       <c r="R21" t="n">
-        <v>7204033</v>
+        <v>7204066</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210255</v>
+        <v>113210240</v>
       </c>
       <c r="B22" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543833</v>
+        <v>544111</v>
       </c>
       <c r="R22" t="n">
-        <v>7204063</v>
+        <v>7204146</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210233</v>
+        <v>113210244</v>
       </c>
       <c r="B23" t="n">
-        <v>77102</v>
+        <v>78133</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3052,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543835</v>
+        <v>543984</v>
       </c>
       <c r="R23" t="n">
-        <v>7204068</v>
+        <v>7204170</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210226</v>
+        <v>113210231</v>
       </c>
       <c r="B24" t="n">
-        <v>79184</v>
+        <v>79230</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3160,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544013</v>
+        <v>543836</v>
       </c>
       <c r="R24" t="n">
-        <v>7204205</v>
+        <v>7204058</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210185</v>
+        <v>113210205</v>
       </c>
       <c r="B25" t="n">
-        <v>74302</v>
+        <v>79223</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3272,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543833</v>
+        <v>543834</v>
       </c>
       <c r="R25" t="n">
-        <v>7204064</v>
+        <v>7204061</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3326,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210230</v>
+        <v>113210252</v>
       </c>
       <c r="B26" t="n">
-        <v>79218</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3384,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543826</v>
+        <v>543761</v>
       </c>
       <c r="R26" t="n">
-        <v>7204074</v>
+        <v>7204153</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3438,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210281</v>
+        <v>113210241</v>
       </c>
       <c r="B27" t="n">
-        <v>79217</v>
+        <v>78133</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,20 +3496,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,10 +3524,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543834</v>
+        <v>544013</v>
       </c>
       <c r="R27" t="n">
-        <v>7204070</v>
+        <v>7204204</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3550,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210252</v>
+        <v>113210202</v>
       </c>
       <c r="B28" t="n">
-        <v>78121</v>
+        <v>56911</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,34 +3612,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543761</v>
+        <v>544006</v>
       </c>
       <c r="R28" t="n">
-        <v>7204153</v>
+        <v>7204169</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3662,7 +3675,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3685,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,10 +3712,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210205</v>
+        <v>113210280</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>86353</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3711,25 +3724,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543834</v>
+        <v>543753</v>
       </c>
       <c r="R29" t="n">
-        <v>7204061</v>
+        <v>7204132</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3774,7 +3787,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3797,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,10 +3824,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210202</v>
+        <v>113210257</v>
       </c>
       <c r="B30" t="n">
-        <v>56910</v>
+        <v>78133</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,38 +3840,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544006</v>
+        <v>543860</v>
       </c>
       <c r="R30" t="n">
-        <v>7204169</v>
+        <v>7204033</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3890,7 +3899,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3900,7 +3909,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,10 +3936,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210244</v>
+        <v>113210248</v>
       </c>
       <c r="B31" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3967,10 +3976,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543984</v>
+        <v>543892</v>
       </c>
       <c r="R31" t="n">
-        <v>7204170</v>
+        <v>7204111</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4002,7 +4011,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4012,7 +4021,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,10 +4048,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210231</v>
+        <v>113210226</v>
       </c>
       <c r="B32" t="n">
-        <v>79218</v>
+        <v>79196</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,25 +4060,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4079,10 +4088,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543836</v>
+        <v>544013</v>
       </c>
       <c r="R32" t="n">
-        <v>7204058</v>
+        <v>7204205</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4114,7 +4123,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4124,7 +4133,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,7 +4163,7 @@
         <v>113210204</v>
       </c>
       <c r="B33" t="n">
-        <v>57362</v>
+        <v>57363</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4272,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210245</v>
+        <v>113210208</v>
       </c>
       <c r="B34" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4288,21 +4297,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4312,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544004</v>
+        <v>543983</v>
       </c>
       <c r="R34" t="n">
-        <v>7204167</v>
+        <v>7204228</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4347,7 +4356,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4357,7 +4366,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4384,10 +4393,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210279</v>
+        <v>113210255</v>
       </c>
       <c r="B35" t="n">
-        <v>81862</v>
+        <v>78133</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4400,21 +4409,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4427,7 +4436,7 @@
         <v>543833</v>
       </c>
       <c r="R35" t="n">
-        <v>7204061</v>
+        <v>7204063</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4459,7 +4468,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4469,7 +4478,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4496,10 +4505,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210215</v>
+        <v>113210254</v>
       </c>
       <c r="B36" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4512,21 +4521,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4536,10 +4545,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543762</v>
+        <v>543828</v>
       </c>
       <c r="R36" t="n">
-        <v>7204149</v>
+        <v>7204074</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4571,7 +4580,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4581,7 +4590,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4608,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210189</v>
+        <v>113210228</v>
       </c>
       <c r="B37" t="n">
-        <v>90045</v>
+        <v>79196</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4624,21 +4633,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4657,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543860</v>
+        <v>544004</v>
       </c>
       <c r="R37" t="n">
-        <v>7204034</v>
+        <v>7204167</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4683,7 +4692,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4693,7 +4702,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4729,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210243</v>
+        <v>113210210</v>
       </c>
       <c r="B38" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,21 +4745,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4760,10 +4769,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543980</v>
+        <v>543984</v>
       </c>
       <c r="R38" t="n">
-        <v>7204203</v>
+        <v>7204167</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4795,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4814,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4832,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210251</v>
+        <v>113210207</v>
       </c>
       <c r="B39" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4848,21 +4857,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4872,10 +4881,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543809</v>
+        <v>544012</v>
       </c>
       <c r="R39" t="n">
-        <v>7204195</v>
+        <v>7204204</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4907,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4917,7 +4926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,10 +4953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210213</v>
+        <v>113210211</v>
       </c>
       <c r="B40" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4984,10 +4993,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543821</v>
+        <v>544004</v>
       </c>
       <c r="R40" t="n">
-        <v>7204193</v>
+        <v>7204168</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5019,7 +5028,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5029,7 +5038,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5056,10 +5065,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210208</v>
+        <v>113210278</v>
       </c>
       <c r="B41" t="n">
-        <v>79185</v>
+        <v>81874</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5072,21 +5081,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5096,10 +5105,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543983</v>
+        <v>543835</v>
       </c>
       <c r="R41" t="n">
-        <v>7204228</v>
+        <v>7204068</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5131,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5141,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,10 +5177,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210207</v>
+        <v>113210245</v>
       </c>
       <c r="B42" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5184,21 +5193,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5208,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544012</v>
+        <v>544004</v>
       </c>
       <c r="R42" t="n">
-        <v>7204204</v>
+        <v>7204167</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5243,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5253,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210184</v>
+        <v>113210243</v>
       </c>
       <c r="B43" t="n">
-        <v>77116</v>
+        <v>78133</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5296,21 +5305,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5320,10 +5329,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543833</v>
+        <v>543980</v>
       </c>
       <c r="R43" t="n">
-        <v>7204064</v>
+        <v>7204203</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5355,7 +5364,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5365,7 +5374,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5392,10 +5401,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210246</v>
+        <v>113210251</v>
       </c>
       <c r="B44" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5432,10 +5441,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543953</v>
+        <v>543809</v>
       </c>
       <c r="R44" t="n">
-        <v>7204079</v>
+        <v>7204195</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5467,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5477,7 +5486,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5504,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210228</v>
+        <v>113210217</v>
       </c>
       <c r="B45" t="n">
-        <v>79184</v>
+        <v>79197</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5520,21 +5529,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5544,10 +5553,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544004</v>
+        <v>543841</v>
       </c>
       <c r="R45" t="n">
-        <v>7204167</v>
+        <v>7204061</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5579,7 +5588,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5589,7 +5598,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210224</v>
+        <v>113210242</v>
       </c>
       <c r="B46" t="n">
-        <v>74307</v>
+        <v>78133</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5632,21 +5641,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5656,10 +5665,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543833</v>
+        <v>543981</v>
       </c>
       <c r="R46" t="n">
-        <v>7204069</v>
+        <v>7204228</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5691,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5701,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210240</v>
+        <v>113210213</v>
       </c>
       <c r="B47" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5744,21 +5753,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5768,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544111</v>
+        <v>543821</v>
       </c>
       <c r="R47" t="n">
-        <v>7204146</v>
+        <v>7204193</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5803,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5813,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5840,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210191</v>
+        <v>113210235</v>
       </c>
       <c r="B48" t="n">
-        <v>56765</v>
+        <v>77490</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5852,47 +5861,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543999</v>
+        <v>543858</v>
       </c>
       <c r="R48" t="n">
-        <v>7204066</v>
+        <v>7204151</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210211</v>
+        <v>113210230</v>
       </c>
       <c r="B49" t="n">
-        <v>79185</v>
+        <v>79230</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5973,25 +5973,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544004</v>
+        <v>543826</v>
       </c>
       <c r="R49" t="n">
-        <v>7204168</v>
+        <v>7204074</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210209</v>
+        <v>113210224</v>
       </c>
       <c r="B50" t="n">
-        <v>79185</v>
+        <v>74319</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543983</v>
+        <v>543833</v>
       </c>
       <c r="R50" t="n">
-        <v>7204203</v>
+        <v>7204069</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210227</v>
+        <v>113210252</v>
       </c>
       <c r="B2" t="n">
-        <v>79196</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543983</v>
+        <v>543761</v>
       </c>
       <c r="R2" t="n">
-        <v>7204228</v>
+        <v>7204153</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210185</v>
+        <v>113210212</v>
       </c>
       <c r="B3" t="n">
-        <v>74314</v>
+        <v>79197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543833</v>
+        <v>543892</v>
       </c>
       <c r="R3" t="n">
-        <v>7204064</v>
+        <v>7204108</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210253</v>
+        <v>113210281</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>79229</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,20 +911,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543753</v>
+        <v>543834</v>
       </c>
       <c r="R4" t="n">
-        <v>7204127</v>
+        <v>7204070</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210281</v>
+        <v>113210191</v>
       </c>
       <c r="B5" t="n">
-        <v>79229</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543834</v>
+        <v>543999</v>
       </c>
       <c r="R5" t="n">
-        <v>7204070</v>
+        <v>7204066</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210233</v>
+        <v>113210240</v>
       </c>
       <c r="B6" t="n">
-        <v>77114</v>
+        <v>78133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543835</v>
+        <v>544111</v>
       </c>
       <c r="R6" t="n">
-        <v>7204068</v>
+        <v>7204146</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210279</v>
+        <v>113210205</v>
       </c>
       <c r="B7" t="n">
-        <v>81874</v>
+        <v>79223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,7 +1284,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543833</v>
+        <v>543834</v>
       </c>
       <c r="R7" t="n">
         <v>7204061</v>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210236</v>
+        <v>113210213</v>
       </c>
       <c r="B8" t="n">
-        <v>78214</v>
+        <v>79197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544118</v>
+        <v>543821</v>
       </c>
       <c r="R8" t="n">
-        <v>7204143</v>
+        <v>7204193</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210184</v>
+        <v>113210280</v>
       </c>
       <c r="B9" t="n">
-        <v>77128</v>
+        <v>86353</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>314</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543833</v>
+        <v>543753</v>
       </c>
       <c r="R9" t="n">
-        <v>7204064</v>
+        <v>7204132</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210189</v>
+        <v>113210211</v>
       </c>
       <c r="B10" t="n">
-        <v>90057</v>
+        <v>79197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543860</v>
+        <v>544004</v>
       </c>
       <c r="R10" t="n">
-        <v>7204034</v>
+        <v>7204168</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210246</v>
+        <v>113210244</v>
       </c>
       <c r="B11" t="n">
         <v>78133</v>
@@ -1723,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543953</v>
+        <v>543984</v>
       </c>
       <c r="R11" t="n">
-        <v>7204079</v>
+        <v>7204170</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210216</v>
+        <v>113210233</v>
       </c>
       <c r="B12" t="n">
-        <v>79197</v>
+        <v>77114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543825</v>
+        <v>543835</v>
       </c>
       <c r="R12" t="n">
-        <v>7204074</v>
+        <v>7204068</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210214</v>
+        <v>113210227</v>
       </c>
       <c r="B13" t="n">
-        <v>79197</v>
+        <v>79196</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543810</v>
+        <v>543983</v>
       </c>
       <c r="R13" t="n">
-        <v>7204198</v>
+        <v>7204228</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,7 +2028,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210250</v>
+        <v>113210256</v>
       </c>
       <c r="B14" t="n">
         <v>78133</v>
@@ -2059,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543822</v>
+        <v>543835</v>
       </c>
       <c r="R14" t="n">
-        <v>7204196</v>
+        <v>7204062</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210249</v>
+        <v>113210209</v>
       </c>
       <c r="B15" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543857</v>
+        <v>543983</v>
       </c>
       <c r="R15" t="n">
-        <v>7204152</v>
+        <v>7204203</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210256</v>
+        <v>113210236</v>
       </c>
       <c r="B16" t="n">
-        <v>78133</v>
+        <v>78214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2268,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543835</v>
+        <v>544118</v>
       </c>
       <c r="R16" t="n">
-        <v>7204062</v>
+        <v>7204143</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210212</v>
+        <v>113210226</v>
       </c>
       <c r="B17" t="n">
-        <v>79197</v>
+        <v>79196</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2380,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543892</v>
+        <v>544013</v>
       </c>
       <c r="R17" t="n">
-        <v>7204108</v>
+        <v>7204205</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2476,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210215</v>
+        <v>113210216</v>
       </c>
       <c r="B18" t="n">
         <v>79197</v>
@@ -2507,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543762</v>
+        <v>543825</v>
       </c>
       <c r="R18" t="n">
-        <v>7204149</v>
+        <v>7204074</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210238</v>
+        <v>113210210</v>
       </c>
       <c r="B19" t="n">
-        <v>90075</v>
+        <v>79197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2604,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543860</v>
+        <v>543984</v>
       </c>
       <c r="R19" t="n">
-        <v>7204033</v>
+        <v>7204167</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210209</v>
+        <v>113210243</v>
       </c>
       <c r="B20" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2716,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,7 +2740,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543983</v>
+        <v>543980</v>
       </c>
       <c r="R20" t="n">
         <v>7204203</v>
@@ -2803,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210191</v>
+        <v>113210241</v>
       </c>
       <c r="B21" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,43 +2828,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543999</v>
+        <v>544013</v>
       </c>
       <c r="R21" t="n">
-        <v>7204066</v>
+        <v>7204204</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210240</v>
+        <v>113210215</v>
       </c>
       <c r="B22" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544111</v>
+        <v>543762</v>
       </c>
       <c r="R22" t="n">
-        <v>7204146</v>
+        <v>7204149</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210244</v>
+        <v>113210207</v>
       </c>
       <c r="B23" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,21 +3052,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543984</v>
+        <v>544012</v>
       </c>
       <c r="R23" t="n">
-        <v>7204170</v>
+        <v>7204204</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210231</v>
+        <v>113210249</v>
       </c>
       <c r="B24" t="n">
-        <v>79230</v>
+        <v>78133</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543836</v>
+        <v>543857</v>
       </c>
       <c r="R24" t="n">
-        <v>7204058</v>
+        <v>7204152</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210205</v>
+        <v>113210255</v>
       </c>
       <c r="B25" t="n">
-        <v>79223</v>
+        <v>78133</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,25 +3272,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543834</v>
+        <v>543833</v>
       </c>
       <c r="R25" t="n">
-        <v>7204061</v>
+        <v>7204063</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,7 +3372,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210252</v>
+        <v>113210248</v>
       </c>
       <c r="B26" t="n">
         <v>78133</v>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543761</v>
+        <v>543892</v>
       </c>
       <c r="R26" t="n">
-        <v>7204153</v>
+        <v>7204111</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210241</v>
+        <v>113210184</v>
       </c>
       <c r="B27" t="n">
-        <v>78133</v>
+        <v>77128</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544013</v>
+        <v>543833</v>
       </c>
       <c r="R27" t="n">
-        <v>7204204</v>
+        <v>7204064</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210202</v>
+        <v>113210214</v>
       </c>
       <c r="B28" t="n">
-        <v>56911</v>
+        <v>79197</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,38 +3612,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544006</v>
+        <v>543810</v>
       </c>
       <c r="R28" t="n">
-        <v>7204169</v>
+        <v>7204198</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3675,7 +3671,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3685,7 +3681,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3712,10 +3708,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210280</v>
+        <v>113210231</v>
       </c>
       <c r="B29" t="n">
-        <v>86353</v>
+        <v>79230</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3724,25 +3720,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3752,10 +3748,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543753</v>
+        <v>543836</v>
       </c>
       <c r="R29" t="n">
-        <v>7204132</v>
+        <v>7204058</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3787,7 +3783,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3797,7 +3793,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3824,10 +3820,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210257</v>
+        <v>113210228</v>
       </c>
       <c r="B30" t="n">
-        <v>78133</v>
+        <v>79196</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3840,21 +3836,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3864,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543860</v>
+        <v>544004</v>
       </c>
       <c r="R30" t="n">
-        <v>7204033</v>
+        <v>7204167</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3899,7 +3895,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3909,7 +3905,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3936,7 +3932,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210248</v>
+        <v>113210253</v>
       </c>
       <c r="B31" t="n">
         <v>78133</v>
@@ -3976,10 +3972,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543892</v>
+        <v>543753</v>
       </c>
       <c r="R31" t="n">
-        <v>7204111</v>
+        <v>7204127</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4011,7 +4007,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4021,7 +4017,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4048,10 +4044,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210226</v>
+        <v>113210238</v>
       </c>
       <c r="B32" t="n">
-        <v>79196</v>
+        <v>90075</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4064,21 +4060,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4088,10 +4084,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544013</v>
+        <v>543860</v>
       </c>
       <c r="R32" t="n">
-        <v>7204205</v>
+        <v>7204033</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4123,7 +4119,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4133,7 +4129,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210204</v>
+        <v>113210189</v>
       </c>
       <c r="B33" t="n">
-        <v>57363</v>
+        <v>90057</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4172,47 +4168,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102125</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543834</v>
+        <v>543860</v>
       </c>
       <c r="R33" t="n">
-        <v>7204061</v>
+        <v>7204034</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4244,7 +4231,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4254,7 +4241,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,10 +4268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210208</v>
+        <v>113210235</v>
       </c>
       <c r="B34" t="n">
-        <v>79197</v>
+        <v>77490</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,25 +4280,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4308,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543983</v>
+        <v>543858</v>
       </c>
       <c r="R34" t="n">
-        <v>7204228</v>
+        <v>7204151</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4356,7 +4343,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4366,7 +4353,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,7 +4380,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210255</v>
+        <v>113210257</v>
       </c>
       <c r="B35" t="n">
         <v>78133</v>
@@ -4433,10 +4420,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543833</v>
+        <v>543860</v>
       </c>
       <c r="R35" t="n">
-        <v>7204063</v>
+        <v>7204033</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4468,7 +4455,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,7 +4465,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4505,10 +4492,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210254</v>
+        <v>113210185</v>
       </c>
       <c r="B36" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4521,21 +4508,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4545,10 +4532,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543828</v>
+        <v>543833</v>
       </c>
       <c r="R36" t="n">
-        <v>7204074</v>
+        <v>7204064</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4580,7 +4567,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4590,7 +4577,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210228</v>
+        <v>113210202</v>
       </c>
       <c r="B37" t="n">
-        <v>79196</v>
+        <v>56911</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4633,34 +4620,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544004</v>
+        <v>544006</v>
       </c>
       <c r="R37" t="n">
-        <v>7204167</v>
+        <v>7204169</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4692,7 +4683,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4702,7 +4693,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,7 +4720,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210210</v>
+        <v>113210217</v>
       </c>
       <c r="B38" t="n">
         <v>79197</v>
@@ -4769,10 +4760,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543984</v>
+        <v>543841</v>
       </c>
       <c r="R38" t="n">
-        <v>7204167</v>
+        <v>7204061</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4804,7 +4795,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,7 +4805,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4832,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210207</v>
+        <v>113210245</v>
       </c>
       <c r="B39" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4857,21 +4848,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4881,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544012</v>
+        <v>544004</v>
       </c>
       <c r="R39" t="n">
-        <v>7204204</v>
+        <v>7204167</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4916,7 +4907,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4926,7 +4917,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4953,10 +4944,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210211</v>
+        <v>113210251</v>
       </c>
       <c r="B40" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4969,21 +4960,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4993,10 +4984,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544004</v>
+        <v>543809</v>
       </c>
       <c r="R40" t="n">
-        <v>7204168</v>
+        <v>7204195</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5028,7 +5019,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5038,7 +5029,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5065,10 +5056,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210278</v>
+        <v>113210246</v>
       </c>
       <c r="B41" t="n">
-        <v>81874</v>
+        <v>78133</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5081,21 +5072,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5105,10 +5096,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543835</v>
+        <v>543953</v>
       </c>
       <c r="R41" t="n">
-        <v>7204068</v>
+        <v>7204079</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5140,7 +5131,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5150,7 +5141,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5177,10 +5168,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210245</v>
+        <v>113210224</v>
       </c>
       <c r="B42" t="n">
-        <v>78133</v>
+        <v>74319</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5193,21 +5184,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5217,10 +5208,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544004</v>
+        <v>543833</v>
       </c>
       <c r="R42" t="n">
-        <v>7204167</v>
+        <v>7204069</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5252,7 +5243,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5253,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5289,10 +5280,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210243</v>
+        <v>113210204</v>
       </c>
       <c r="B43" t="n">
-        <v>78133</v>
+        <v>57363</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5301,38 +5292,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543980</v>
+        <v>543834</v>
       </c>
       <c r="R43" t="n">
-        <v>7204203</v>
+        <v>7204061</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5401,7 +5401,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210251</v>
+        <v>113210254</v>
       </c>
       <c r="B44" t="n">
         <v>78133</v>
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543809</v>
+        <v>543828</v>
       </c>
       <c r="R44" t="n">
-        <v>7204195</v>
+        <v>7204074</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5513,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210217</v>
+        <v>113210278</v>
       </c>
       <c r="B45" t="n">
-        <v>79197</v>
+        <v>81874</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5529,21 +5529,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543841</v>
+        <v>543835</v>
       </c>
       <c r="R45" t="n">
-        <v>7204061</v>
+        <v>7204068</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210242</v>
+        <v>113210279</v>
       </c>
       <c r="B46" t="n">
-        <v>78133</v>
+        <v>81874</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543981</v>
+        <v>543833</v>
       </c>
       <c r="R46" t="n">
-        <v>7204228</v>
+        <v>7204061</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210213</v>
+        <v>113210242</v>
       </c>
       <c r="B47" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5753,21 +5753,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543821</v>
+        <v>543981</v>
       </c>
       <c r="R47" t="n">
-        <v>7204193</v>
+        <v>7204228</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210235</v>
+        <v>113210250</v>
       </c>
       <c r="B48" t="n">
-        <v>77490</v>
+        <v>78133</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5861,25 +5861,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543858</v>
+        <v>543822</v>
       </c>
       <c r="R48" t="n">
-        <v>7204151</v>
+        <v>7204196</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210230</v>
+        <v>113210208</v>
       </c>
       <c r="B49" t="n">
-        <v>79230</v>
+        <v>79197</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5973,25 +5973,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543826</v>
+        <v>543983</v>
       </c>
       <c r="R49" t="n">
-        <v>7204074</v>
+        <v>7204228</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210224</v>
+        <v>113210230</v>
       </c>
       <c r="B50" t="n">
-        <v>74319</v>
+        <v>79230</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6085,25 +6085,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1467</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543833</v>
+        <v>543826</v>
       </c>
       <c r="R50" t="n">
-        <v>7204069</v>
+        <v>7204074</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210212</v>
+        <v>113210281</v>
       </c>
       <c r="B3" t="n">
-        <v>79197</v>
+        <v>79229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543892</v>
+        <v>543834</v>
       </c>
       <c r="R3" t="n">
-        <v>7204108</v>
+        <v>7204070</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210281</v>
+        <v>113210191</v>
       </c>
       <c r="B4" t="n">
-        <v>79229</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543834</v>
+        <v>543999</v>
       </c>
       <c r="R4" t="n">
-        <v>7204070</v>
+        <v>7204066</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210191</v>
+        <v>113210212</v>
       </c>
       <c r="B5" t="n">
-        <v>56766</v>
+        <v>79197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543999</v>
+        <v>543892</v>
       </c>
       <c r="R5" t="n">
-        <v>7204066</v>
+        <v>7204108</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210217</v>
+        <v>113210245</v>
       </c>
       <c r="B38" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,21 +4736,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543841</v>
+        <v>544004</v>
       </c>
       <c r="R38" t="n">
-        <v>7204061</v>
+        <v>7204167</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4832,7 +4832,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210245</v>
+        <v>113210251</v>
       </c>
       <c r="B39" t="n">
         <v>78133</v>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544004</v>
+        <v>543809</v>
       </c>
       <c r="R39" t="n">
-        <v>7204167</v>
+        <v>7204195</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,10 +4944,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210251</v>
+        <v>113210217</v>
       </c>
       <c r="B40" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4960,21 +4960,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543809</v>
+        <v>543841</v>
       </c>
       <c r="R40" t="n">
-        <v>7204195</v>
+        <v>7204061</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210279</v>
+        <v>113210208</v>
       </c>
       <c r="B46" t="n">
-        <v>81874</v>
+        <v>79197</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543833</v>
+        <v>543983</v>
       </c>
       <c r="R46" t="n">
-        <v>7204061</v>
+        <v>7204228</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210242</v>
+        <v>113210230</v>
       </c>
       <c r="B47" t="n">
-        <v>78133</v>
+        <v>79230</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543981</v>
+        <v>543826</v>
       </c>
       <c r="R47" t="n">
-        <v>7204228</v>
+        <v>7204074</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210250</v>
+        <v>113210279</v>
       </c>
       <c r="B48" t="n">
-        <v>78133</v>
+        <v>81874</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543822</v>
+        <v>543833</v>
       </c>
       <c r="R48" t="n">
-        <v>7204196</v>
+        <v>7204061</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210208</v>
+        <v>113210242</v>
       </c>
       <c r="B49" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543983</v>
+        <v>543981</v>
       </c>
       <c r="R49" t="n">
         <v>7204228</v>
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210230</v>
+        <v>113210250</v>
       </c>
       <c r="B50" t="n">
-        <v>79230</v>
+        <v>78133</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6085,25 +6085,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543826</v>
+        <v>543822</v>
       </c>
       <c r="R50" t="n">
-        <v>7204074</v>
+        <v>7204196</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210252</v>
+        <v>113210204</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>57363</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543761</v>
+        <v>543834</v>
       </c>
       <c r="R2" t="n">
-        <v>7204153</v>
+        <v>7204061</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210281</v>
+        <v>113210248</v>
       </c>
       <c r="B3" t="n">
-        <v>79229</v>
+        <v>78155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543834</v>
+        <v>543892</v>
       </c>
       <c r="R3" t="n">
-        <v>7204070</v>
+        <v>7204111</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210191</v>
+        <v>113210281</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>79251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543999</v>
+        <v>543834</v>
       </c>
       <c r="R4" t="n">
-        <v>7204066</v>
+        <v>7204070</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210212</v>
+        <v>113210255</v>
       </c>
       <c r="B5" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543892</v>
+        <v>543833</v>
       </c>
       <c r="R5" t="n">
-        <v>7204108</v>
+        <v>7204063</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210240</v>
+        <v>113210212</v>
       </c>
       <c r="B6" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544111</v>
+        <v>543892</v>
       </c>
       <c r="R6" t="n">
-        <v>7204146</v>
+        <v>7204108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210205</v>
+        <v>113210228</v>
       </c>
       <c r="B7" t="n">
-        <v>79223</v>
+        <v>79218</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543834</v>
+        <v>544004</v>
       </c>
       <c r="R7" t="n">
-        <v>7204061</v>
+        <v>7204167</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210213</v>
+        <v>113210254</v>
       </c>
       <c r="B8" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543821</v>
+        <v>543828</v>
       </c>
       <c r="R8" t="n">
-        <v>7204193</v>
+        <v>7204074</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210280</v>
+        <v>113210252</v>
       </c>
       <c r="B9" t="n">
-        <v>86353</v>
+        <v>78155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543753</v>
+        <v>543761</v>
       </c>
       <c r="R9" t="n">
-        <v>7204132</v>
+        <v>7204153</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210211</v>
+        <v>113210210</v>
       </c>
       <c r="B10" t="n">
-        <v>79197</v>
+        <v>79219</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544004</v>
+        <v>543984</v>
       </c>
       <c r="R10" t="n">
-        <v>7204168</v>
+        <v>7204167</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210244</v>
+        <v>113210240</v>
       </c>
       <c r="B11" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543984</v>
+        <v>544111</v>
       </c>
       <c r="R11" t="n">
-        <v>7204170</v>
+        <v>7204146</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210233</v>
+        <v>113210245</v>
       </c>
       <c r="B12" t="n">
-        <v>77114</v>
+        <v>78155</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543835</v>
+        <v>544004</v>
       </c>
       <c r="R12" t="n">
-        <v>7204068</v>
+        <v>7204167</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210227</v>
+        <v>113210250</v>
       </c>
       <c r="B13" t="n">
-        <v>79196</v>
+        <v>78155</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543983</v>
+        <v>543822</v>
       </c>
       <c r="R13" t="n">
-        <v>7204228</v>
+        <v>7204196</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210256</v>
+        <v>113210185</v>
       </c>
       <c r="B14" t="n">
-        <v>78133</v>
+        <v>74336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543835</v>
+        <v>543833</v>
       </c>
       <c r="R14" t="n">
-        <v>7204062</v>
+        <v>7204064</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210209</v>
+        <v>113210184</v>
       </c>
       <c r="B15" t="n">
-        <v>79197</v>
+        <v>77150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543983</v>
+        <v>543833</v>
       </c>
       <c r="R15" t="n">
-        <v>7204203</v>
+        <v>7204064</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210236</v>
+        <v>113210213</v>
       </c>
       <c r="B16" t="n">
-        <v>78214</v>
+        <v>79219</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,21 +2268,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544118</v>
+        <v>543821</v>
       </c>
       <c r="R16" t="n">
-        <v>7204143</v>
+        <v>7204193</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210226</v>
+        <v>113210246</v>
       </c>
       <c r="B17" t="n">
-        <v>79196</v>
+        <v>78155</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,21 +2380,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544013</v>
+        <v>543953</v>
       </c>
       <c r="R17" t="n">
-        <v>7204205</v>
+        <v>7204079</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210216</v>
+        <v>113210256</v>
       </c>
       <c r="B18" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543825</v>
+        <v>543835</v>
       </c>
       <c r="R18" t="n">
-        <v>7204074</v>
+        <v>7204062</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210210</v>
+        <v>113210214</v>
       </c>
       <c r="B19" t="n">
-        <v>79197</v>
+        <v>79219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543984</v>
+        <v>543810</v>
       </c>
       <c r="R19" t="n">
-        <v>7204167</v>
+        <v>7204198</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210243</v>
+        <v>113210233</v>
       </c>
       <c r="B20" t="n">
-        <v>78133</v>
+        <v>77136</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543980</v>
+        <v>543835</v>
       </c>
       <c r="R20" t="n">
-        <v>7204203</v>
+        <v>7204068</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210241</v>
+        <v>113210280</v>
       </c>
       <c r="B21" t="n">
-        <v>78133</v>
+        <v>86375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,21 +2828,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544013</v>
+        <v>543753</v>
       </c>
       <c r="R21" t="n">
-        <v>7204204</v>
+        <v>7204132</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210215</v>
+        <v>113210231</v>
       </c>
       <c r="B22" t="n">
-        <v>79197</v>
+        <v>79252</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543762</v>
+        <v>543836</v>
       </c>
       <c r="R22" t="n">
-        <v>7204149</v>
+        <v>7204058</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210207</v>
+        <v>113210227</v>
       </c>
       <c r="B23" t="n">
-        <v>79197</v>
+        <v>79218</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,21 +3052,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544012</v>
+        <v>543983</v>
       </c>
       <c r="R23" t="n">
-        <v>7204204</v>
+        <v>7204228</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210249</v>
+        <v>113210230</v>
       </c>
       <c r="B24" t="n">
-        <v>78133</v>
+        <v>79252</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543857</v>
+        <v>543826</v>
       </c>
       <c r="R24" t="n">
-        <v>7204152</v>
+        <v>7204074</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210255</v>
+        <v>113210235</v>
       </c>
       <c r="B25" t="n">
-        <v>78133</v>
+        <v>77512</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,25 +3272,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543833</v>
+        <v>543858</v>
       </c>
       <c r="R25" t="n">
-        <v>7204063</v>
+        <v>7204151</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210248</v>
+        <v>113210226</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>79218</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3388,21 +3388,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543892</v>
+        <v>544013</v>
       </c>
       <c r="R26" t="n">
-        <v>7204111</v>
+        <v>7204205</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210184</v>
+        <v>113210249</v>
       </c>
       <c r="B27" t="n">
-        <v>77128</v>
+        <v>78155</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,21 +3500,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543833</v>
+        <v>543857</v>
       </c>
       <c r="R27" t="n">
-        <v>7204064</v>
+        <v>7204152</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210214</v>
+        <v>113210242</v>
       </c>
       <c r="B28" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543810</v>
+        <v>543981</v>
       </c>
       <c r="R28" t="n">
-        <v>7204198</v>
+        <v>7204228</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210231</v>
+        <v>113210209</v>
       </c>
       <c r="B29" t="n">
-        <v>79230</v>
+        <v>79219</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,25 +3720,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543836</v>
+        <v>543983</v>
       </c>
       <c r="R29" t="n">
-        <v>7204058</v>
+        <v>7204203</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3820,10 +3820,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210228</v>
+        <v>113210216</v>
       </c>
       <c r="B30" t="n">
-        <v>79196</v>
+        <v>79219</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,21 +3836,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544004</v>
+        <v>543825</v>
       </c>
       <c r="R30" t="n">
-        <v>7204167</v>
+        <v>7204074</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210253</v>
+        <v>113210191</v>
       </c>
       <c r="B31" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3948,34 +3948,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543753</v>
+        <v>543999</v>
       </c>
       <c r="R31" t="n">
-        <v>7204127</v>
+        <v>7204066</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4007,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4017,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4044,10 +4053,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210238</v>
+        <v>113210241</v>
       </c>
       <c r="B32" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4060,21 +4069,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4084,10 +4093,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543860</v>
+        <v>544013</v>
       </c>
       <c r="R32" t="n">
-        <v>7204033</v>
+        <v>7204204</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4119,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4129,7 +4138,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210189</v>
+        <v>113210243</v>
       </c>
       <c r="B33" t="n">
-        <v>90057</v>
+        <v>78155</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4172,21 +4181,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4196,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543860</v>
+        <v>543980</v>
       </c>
       <c r="R33" t="n">
-        <v>7204034</v>
+        <v>7204203</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4231,7 +4240,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4241,7 +4250,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4268,10 +4277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210235</v>
+        <v>113210236</v>
       </c>
       <c r="B34" t="n">
-        <v>77490</v>
+        <v>78236</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,25 +4289,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>498</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4308,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543858</v>
+        <v>544118</v>
       </c>
       <c r="R34" t="n">
-        <v>7204151</v>
+        <v>7204143</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4343,7 +4352,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4353,7 +4362,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210257</v>
+        <v>113210251</v>
       </c>
       <c r="B35" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4420,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543860</v>
+        <v>543809</v>
       </c>
       <c r="R35" t="n">
-        <v>7204033</v>
+        <v>7204195</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4455,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4465,7 +4474,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210185</v>
+        <v>113210205</v>
       </c>
       <c r="B36" t="n">
-        <v>74314</v>
+        <v>79245</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,25 +4513,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4532,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543833</v>
+        <v>543834</v>
       </c>
       <c r="R36" t="n">
-        <v>7204064</v>
+        <v>7204061</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4567,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4577,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210202</v>
+        <v>113210217</v>
       </c>
       <c r="B37" t="n">
-        <v>56911</v>
+        <v>79219</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4620,38 +4629,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544006</v>
+        <v>543841</v>
       </c>
       <c r="R37" t="n">
-        <v>7204169</v>
+        <v>7204061</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4683,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4693,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210245</v>
+        <v>113210238</v>
       </c>
       <c r="B38" t="n">
-        <v>78133</v>
+        <v>90097</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,21 +4741,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4760,10 +4765,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544004</v>
+        <v>543860</v>
       </c>
       <c r="R38" t="n">
-        <v>7204167</v>
+        <v>7204033</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4795,7 +4800,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4810,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4832,10 +4837,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210251</v>
+        <v>113210253</v>
       </c>
       <c r="B39" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4872,10 +4877,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543809</v>
+        <v>543753</v>
       </c>
       <c r="R39" t="n">
-        <v>7204195</v>
+        <v>7204127</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4907,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4917,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,10 +4949,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210217</v>
+        <v>113210215</v>
       </c>
       <c r="B40" t="n">
-        <v>79197</v>
+        <v>79219</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4984,10 +4989,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543841</v>
+        <v>543762</v>
       </c>
       <c r="R40" t="n">
-        <v>7204061</v>
+        <v>7204149</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5019,7 +5024,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5029,7 +5034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5056,10 +5061,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210246</v>
+        <v>113210244</v>
       </c>
       <c r="B41" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5096,10 +5101,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543953</v>
+        <v>543984</v>
       </c>
       <c r="R41" t="n">
-        <v>7204079</v>
+        <v>7204170</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5131,7 +5136,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5141,7 +5146,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210224</v>
+        <v>113210208</v>
       </c>
       <c r="B42" t="n">
-        <v>74319</v>
+        <v>79219</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5184,21 +5189,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5208,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543833</v>
+        <v>543983</v>
       </c>
       <c r="R42" t="n">
-        <v>7204069</v>
+        <v>7204228</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5243,7 +5248,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5253,7 +5258,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,10 +5285,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210204</v>
+        <v>113210279</v>
       </c>
       <c r="B43" t="n">
-        <v>57363</v>
+        <v>81896</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5292,44 +5297,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102125</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543834</v>
+        <v>543833</v>
       </c>
       <c r="R43" t="n">
         <v>7204061</v>
@@ -5364,7 +5360,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5374,7 +5370,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5401,10 +5397,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210254</v>
+        <v>113210278</v>
       </c>
       <c r="B44" t="n">
-        <v>78133</v>
+        <v>81896</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5417,21 +5413,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5441,10 +5437,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543828</v>
+        <v>543835</v>
       </c>
       <c r="R44" t="n">
-        <v>7204074</v>
+        <v>7204068</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5476,7 +5472,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5486,7 +5482,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5513,10 +5509,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210278</v>
+        <v>113210257</v>
       </c>
       <c r="B45" t="n">
-        <v>81874</v>
+        <v>78155</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5529,21 +5525,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5553,10 +5549,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543835</v>
+        <v>543860</v>
       </c>
       <c r="R45" t="n">
-        <v>7204068</v>
+        <v>7204033</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5588,7 +5584,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5598,7 +5594,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5625,10 +5621,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210208</v>
+        <v>113210202</v>
       </c>
       <c r="B46" t="n">
-        <v>79197</v>
+        <v>56911</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5641,34 +5637,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543983</v>
+        <v>544006</v>
       </c>
       <c r="R46" t="n">
-        <v>7204228</v>
+        <v>7204169</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210230</v>
+        <v>113210224</v>
       </c>
       <c r="B47" t="n">
-        <v>79230</v>
+        <v>74341</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,25 +5749,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>1467</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543826</v>
+        <v>543833</v>
       </c>
       <c r="R47" t="n">
-        <v>7204074</v>
+        <v>7204069</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210279</v>
+        <v>113210211</v>
       </c>
       <c r="B48" t="n">
-        <v>81874</v>
+        <v>79219</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543833</v>
+        <v>544004</v>
       </c>
       <c r="R48" t="n">
-        <v>7204061</v>
+        <v>7204168</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210242</v>
+        <v>113210189</v>
       </c>
       <c r="B49" t="n">
-        <v>78133</v>
+        <v>90079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543981</v>
+        <v>543860</v>
       </c>
       <c r="R49" t="n">
-        <v>7204228</v>
+        <v>7204034</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210250</v>
+        <v>113210207</v>
       </c>
       <c r="B50" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543822</v>
+        <v>544012</v>
       </c>
       <c r="R50" t="n">
-        <v>7204196</v>
+        <v>7204204</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210230</v>
+        <v>113210235</v>
       </c>
       <c r="B24" t="n">
-        <v>79252</v>
+        <v>77512</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543826</v>
+        <v>543858</v>
       </c>
       <c r="R24" t="n">
-        <v>7204074</v>
+        <v>7204151</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210235</v>
+        <v>113210226</v>
       </c>
       <c r="B25" t="n">
-        <v>77512</v>
+        <v>79218</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,25 +3272,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>498</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543858</v>
+        <v>544013</v>
       </c>
       <c r="R25" t="n">
-        <v>7204151</v>
+        <v>7204205</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210226</v>
+        <v>113210230</v>
       </c>
       <c r="B26" t="n">
-        <v>79218</v>
+        <v>79252</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,25 +3384,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544013</v>
+        <v>543826</v>
       </c>
       <c r="R26" t="n">
-        <v>7204205</v>
+        <v>7204074</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3820,10 +3820,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210216</v>
+        <v>113210241</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>78155</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,21 +3836,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543825</v>
+        <v>544013</v>
       </c>
       <c r="R30" t="n">
-        <v>7204074</v>
+        <v>7204204</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210191</v>
+        <v>113210243</v>
       </c>
       <c r="B31" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3948,43 +3948,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543999</v>
+        <v>543980</v>
       </c>
       <c r="R31" t="n">
-        <v>7204066</v>
+        <v>7204203</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4016,7 +4007,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4017,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,10 +4044,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210241</v>
+        <v>113210216</v>
       </c>
       <c r="B32" t="n">
-        <v>78155</v>
+        <v>79219</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4069,21 +4060,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4093,10 +4084,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544013</v>
+        <v>543825</v>
       </c>
       <c r="R32" t="n">
-        <v>7204204</v>
+        <v>7204074</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4128,7 +4119,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4138,7 +4129,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210243</v>
+        <v>113210191</v>
       </c>
       <c r="B33" t="n">
-        <v>78155</v>
+        <v>56766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,34 +4172,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543980</v>
+        <v>543999</v>
       </c>
       <c r="R33" t="n">
-        <v>7204203</v>
+        <v>7204066</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210204</v>
+        <v>113210278</v>
       </c>
       <c r="B2" t="n">
-        <v>57363</v>
+        <v>81900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543834</v>
+        <v>543835</v>
       </c>
       <c r="R2" t="n">
-        <v>7204061</v>
+        <v>7204068</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210248</v>
+        <v>113210214</v>
       </c>
       <c r="B3" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543892</v>
+        <v>543810</v>
       </c>
       <c r="R3" t="n">
-        <v>7204111</v>
+        <v>7204198</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210281</v>
+        <v>113210252</v>
       </c>
       <c r="B4" t="n">
-        <v>79251</v>
+        <v>78158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,20 +911,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543834</v>
+        <v>543761</v>
       </c>
       <c r="R4" t="n">
-        <v>7204070</v>
+        <v>7204153</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210255</v>
+        <v>113210217</v>
       </c>
       <c r="B5" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543833</v>
+        <v>543841</v>
       </c>
       <c r="R5" t="n">
-        <v>7204063</v>
+        <v>7204061</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210212</v>
+        <v>113210231</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79256</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543892</v>
+        <v>543836</v>
       </c>
       <c r="R6" t="n">
-        <v>7204108</v>
+        <v>7204058</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210228</v>
+        <v>113210238</v>
       </c>
       <c r="B7" t="n">
-        <v>79218</v>
+        <v>90101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544004</v>
+        <v>543860</v>
       </c>
       <c r="R7" t="n">
-        <v>7204167</v>
+        <v>7204033</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210254</v>
+        <v>113210208</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543828</v>
+        <v>543983</v>
       </c>
       <c r="R8" t="n">
-        <v>7204074</v>
+        <v>7204228</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210252</v>
+        <v>113210256</v>
       </c>
       <c r="B9" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543761</v>
+        <v>543835</v>
       </c>
       <c r="R9" t="n">
-        <v>7204153</v>
+        <v>7204062</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210210</v>
+        <v>113210255</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543984</v>
+        <v>543833</v>
       </c>
       <c r="R10" t="n">
-        <v>7204167</v>
+        <v>7204063</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210240</v>
+        <v>113210233</v>
       </c>
       <c r="B11" t="n">
-        <v>78155</v>
+        <v>77139</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544111</v>
+        <v>543835</v>
       </c>
       <c r="R11" t="n">
-        <v>7204146</v>
+        <v>7204068</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210245</v>
+        <v>113210240</v>
       </c>
       <c r="B12" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544004</v>
+        <v>544111</v>
       </c>
       <c r="R12" t="n">
-        <v>7204167</v>
+        <v>7204146</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,7 +1910,7 @@
         <v>113210250</v>
       </c>
       <c r="B13" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210185</v>
+        <v>113210281</v>
       </c>
       <c r="B14" t="n">
-        <v>74336</v>
+        <v>79255</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543833</v>
+        <v>543834</v>
       </c>
       <c r="R14" t="n">
-        <v>7204064</v>
+        <v>7204070</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210184</v>
+        <v>113210224</v>
       </c>
       <c r="B15" t="n">
-        <v>77150</v>
+        <v>74344</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>314</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,7 +2174,7 @@
         <v>543833</v>
       </c>
       <c r="R15" t="n">
-        <v>7204064</v>
+        <v>7204069</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210213</v>
+        <v>113210202</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>56914</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,34 +2259,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543821</v>
+        <v>544006</v>
       </c>
       <c r="R16" t="n">
-        <v>7204193</v>
+        <v>7204169</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210246</v>
+        <v>113210279</v>
       </c>
       <c r="B17" t="n">
-        <v>78155</v>
+        <v>81900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543953</v>
+        <v>543833</v>
       </c>
       <c r="R17" t="n">
-        <v>7204079</v>
+        <v>7204061</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210256</v>
+        <v>113210212</v>
       </c>
       <c r="B18" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2487,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543835</v>
+        <v>543892</v>
       </c>
       <c r="R18" t="n">
-        <v>7204062</v>
+        <v>7204108</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210214</v>
+        <v>113210184</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>77153</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543810</v>
+        <v>543833</v>
       </c>
       <c r="R19" t="n">
-        <v>7204198</v>
+        <v>7204064</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210233</v>
+        <v>113210189</v>
       </c>
       <c r="B20" t="n">
-        <v>77136</v>
+        <v>90083</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543835</v>
+        <v>543860</v>
       </c>
       <c r="R20" t="n">
-        <v>7204068</v>
+        <v>7204034</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210280</v>
+        <v>113210191</v>
       </c>
       <c r="B21" t="n">
-        <v>86375</v>
+        <v>56769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,34 +2823,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543753</v>
+        <v>543999</v>
       </c>
       <c r="R21" t="n">
-        <v>7204132</v>
+        <v>7204066</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210231</v>
+        <v>113210185</v>
       </c>
       <c r="B22" t="n">
-        <v>79252</v>
+        <v>74339</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2940,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543836</v>
+        <v>543833</v>
       </c>
       <c r="R22" t="n">
-        <v>7204058</v>
+        <v>7204064</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210227</v>
+        <v>113210204</v>
       </c>
       <c r="B23" t="n">
-        <v>79218</v>
+        <v>57366</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,38 +3052,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543983</v>
+        <v>543834</v>
       </c>
       <c r="R23" t="n">
-        <v>7204228</v>
+        <v>7204061</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3124,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3134,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3161,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210235</v>
+        <v>113210280</v>
       </c>
       <c r="B24" t="n">
-        <v>77512</v>
+        <v>86379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,25 +3173,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3201,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543858</v>
+        <v>543753</v>
       </c>
       <c r="R24" t="n">
-        <v>7204151</v>
+        <v>7204132</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3236,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3246,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210226</v>
+        <v>113210248</v>
       </c>
       <c r="B25" t="n">
-        <v>79218</v>
+        <v>78158</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,21 +3289,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544013</v>
+        <v>543892</v>
       </c>
       <c r="R25" t="n">
-        <v>7204205</v>
+        <v>7204111</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3348,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3358,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3385,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210230</v>
+        <v>113210249</v>
       </c>
       <c r="B26" t="n">
-        <v>79252</v>
+        <v>78158</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,25 +3397,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3425,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543826</v>
+        <v>543857</v>
       </c>
       <c r="R26" t="n">
-        <v>7204074</v>
+        <v>7204152</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3447,7 +3460,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3470,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210249</v>
+        <v>113210211</v>
       </c>
       <c r="B27" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,21 +3513,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3524,10 +3537,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543857</v>
+        <v>544004</v>
       </c>
       <c r="R27" t="n">
-        <v>7204152</v>
+        <v>7204168</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3559,7 +3572,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3582,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,10 +3609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210242</v>
+        <v>113210213</v>
       </c>
       <c r="B28" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,21 +3625,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3636,10 +3649,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543981</v>
+        <v>543821</v>
       </c>
       <c r="R28" t="n">
-        <v>7204228</v>
+        <v>7204193</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3671,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3681,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210209</v>
+        <v>113210243</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3724,21 +3737,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3748,7 +3761,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543983</v>
+        <v>543980</v>
       </c>
       <c r="R29" t="n">
         <v>7204203</v>
@@ -3820,10 +3833,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210241</v>
+        <v>113210216</v>
       </c>
       <c r="B30" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,21 +3849,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544013</v>
+        <v>543825</v>
       </c>
       <c r="R30" t="n">
-        <v>7204204</v>
+        <v>7204074</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3895,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3905,7 +3918,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210243</v>
+        <v>113210207</v>
       </c>
       <c r="B31" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3948,21 +3961,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3972,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543980</v>
+        <v>544012</v>
       </c>
       <c r="R31" t="n">
-        <v>7204203</v>
+        <v>7204204</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4007,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4017,7 +4030,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210216</v>
+        <v>113210209</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543825</v>
+        <v>543983</v>
       </c>
       <c r="R32" t="n">
-        <v>7204074</v>
+        <v>7204203</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4119,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4129,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,10 +4169,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210191</v>
+        <v>113210228</v>
       </c>
       <c r="B33" t="n">
-        <v>56766</v>
+        <v>79222</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4172,43 +4185,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543999</v>
+        <v>544004</v>
       </c>
       <c r="R33" t="n">
-        <v>7204066</v>
+        <v>7204167</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4240,7 +4244,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4250,7 +4254,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4277,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210236</v>
+        <v>113210245</v>
       </c>
       <c r="B34" t="n">
-        <v>78236</v>
+        <v>78158</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,21 +4297,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4317,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544118</v>
+        <v>544004</v>
       </c>
       <c r="R34" t="n">
-        <v>7204143</v>
+        <v>7204167</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4352,7 +4356,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,7 +4366,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,7 +4396,7 @@
         <v>113210251</v>
       </c>
       <c r="B35" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,10 +4505,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210205</v>
+        <v>113210244</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>78158</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4513,25 +4517,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4541,10 +4545,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543834</v>
+        <v>543984</v>
       </c>
       <c r="R36" t="n">
-        <v>7204061</v>
+        <v>7204170</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4586,7 +4590,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210217</v>
+        <v>113210257</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4629,21 +4633,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4653,10 +4657,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543841</v>
+        <v>543860</v>
       </c>
       <c r="R37" t="n">
-        <v>7204061</v>
+        <v>7204033</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4688,7 +4692,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4702,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,10 +4729,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210238</v>
+        <v>113210253</v>
       </c>
       <c r="B38" t="n">
-        <v>90097</v>
+        <v>78158</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4741,21 +4745,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4765,10 +4769,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543860</v>
+        <v>543753</v>
       </c>
       <c r="R38" t="n">
-        <v>7204033</v>
+        <v>7204127</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4800,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4810,7 +4814,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210253</v>
+        <v>113210230</v>
       </c>
       <c r="B39" t="n">
-        <v>78155</v>
+        <v>79256</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4849,25 +4853,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4877,10 +4881,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543753</v>
+        <v>543826</v>
       </c>
       <c r="R39" t="n">
-        <v>7204127</v>
+        <v>7204074</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4912,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4922,7 +4926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4949,10 +4953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210215</v>
+        <v>113210205</v>
       </c>
       <c r="B40" t="n">
-        <v>79219</v>
+        <v>79249</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4961,25 +4965,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4989,10 +4993,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543762</v>
+        <v>543834</v>
       </c>
       <c r="R40" t="n">
-        <v>7204149</v>
+        <v>7204061</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5024,7 +5028,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,7 +5038,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5061,10 +5065,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210244</v>
+        <v>113210210</v>
       </c>
       <c r="B41" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5077,21 +5081,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5104,7 +5108,7 @@
         <v>543984</v>
       </c>
       <c r="R41" t="n">
-        <v>7204170</v>
+        <v>7204167</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5173,10 +5177,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210208</v>
+        <v>113210226</v>
       </c>
       <c r="B42" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5189,21 +5193,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5213,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543983</v>
+        <v>544013</v>
       </c>
       <c r="R42" t="n">
-        <v>7204228</v>
+        <v>7204205</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5248,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5258,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5285,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210279</v>
+        <v>113210235</v>
       </c>
       <c r="B43" t="n">
-        <v>81896</v>
+        <v>77515</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5297,25 +5301,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5325,10 +5329,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543833</v>
+        <v>543858</v>
       </c>
       <c r="R43" t="n">
-        <v>7204061</v>
+        <v>7204151</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5370,7 +5374,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5397,10 +5401,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210278</v>
+        <v>113210246</v>
       </c>
       <c r="B44" t="n">
-        <v>81896</v>
+        <v>78158</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5413,21 +5417,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5437,10 +5441,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543835</v>
+        <v>543953</v>
       </c>
       <c r="R44" t="n">
-        <v>7204068</v>
+        <v>7204079</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5472,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5482,7 +5486,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5509,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210257</v>
+        <v>113210215</v>
       </c>
       <c r="B45" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5525,21 +5529,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5549,10 +5553,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543860</v>
+        <v>543762</v>
       </c>
       <c r="R45" t="n">
-        <v>7204033</v>
+        <v>7204149</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5584,7 +5588,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5621,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210202</v>
+        <v>113210241</v>
       </c>
       <c r="B46" t="n">
-        <v>56911</v>
+        <v>78158</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5637,38 +5641,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544006</v>
+        <v>544013</v>
       </c>
       <c r="R46" t="n">
-        <v>7204169</v>
+        <v>7204204</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210224</v>
+        <v>113210242</v>
       </c>
       <c r="B47" t="n">
-        <v>74341</v>
+        <v>78158</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5753,21 +5753,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543833</v>
+        <v>543981</v>
       </c>
       <c r="R47" t="n">
-        <v>7204069</v>
+        <v>7204228</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210211</v>
+        <v>113210254</v>
       </c>
       <c r="B48" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544004</v>
+        <v>543828</v>
       </c>
       <c r="R48" t="n">
-        <v>7204168</v>
+        <v>7204074</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210189</v>
+        <v>113210236</v>
       </c>
       <c r="B49" t="n">
-        <v>90079</v>
+        <v>78240</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543860</v>
+        <v>544118</v>
       </c>
       <c r="R49" t="n">
-        <v>7204034</v>
+        <v>7204143</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210207</v>
+        <v>113210227</v>
       </c>
       <c r="B50" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544012</v>
+        <v>543983</v>
       </c>
       <c r="R50" t="n">
-        <v>7204204</v>
+        <v>7204228</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210252</v>
+        <v>113210217</v>
       </c>
       <c r="B4" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543761</v>
+        <v>543841</v>
       </c>
       <c r="R4" t="n">
-        <v>7204153</v>
+        <v>7204061</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210217</v>
+        <v>113210252</v>
       </c>
       <c r="B5" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543841</v>
+        <v>543761</v>
       </c>
       <c r="R5" t="n">
-        <v>7204061</v>
+        <v>7204153</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2807,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210191</v>
+        <v>113210185</v>
       </c>
       <c r="B21" t="n">
-        <v>56769</v>
+        <v>74339</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,43 +2823,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543999</v>
+        <v>543833</v>
       </c>
       <c r="R21" t="n">
-        <v>7204066</v>
+        <v>7204064</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210185</v>
+        <v>113210191</v>
       </c>
       <c r="B22" t="n">
-        <v>74339</v>
+        <v>56769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2944,34 +2935,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543833</v>
+        <v>543999</v>
       </c>
       <c r="R22" t="n">
-        <v>7204064</v>
+        <v>7204066</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -5065,10 +5065,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210210</v>
+        <v>113210235</v>
       </c>
       <c r="B41" t="n">
-        <v>79223</v>
+        <v>77515</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5077,25 +5077,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543984</v>
+        <v>543858</v>
       </c>
       <c r="R41" t="n">
-        <v>7204167</v>
+        <v>7204151</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210235</v>
+        <v>113210210</v>
       </c>
       <c r="B43" t="n">
-        <v>77515</v>
+        <v>79223</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5301,25 +5301,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543858</v>
+        <v>543984</v>
       </c>
       <c r="R43" t="n">
-        <v>7204151</v>
+        <v>7204167</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210241</v>
+        <v>113210236</v>
       </c>
       <c r="B46" t="n">
-        <v>78158</v>
+        <v>78240</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544013</v>
+        <v>544118</v>
       </c>
       <c r="R46" t="n">
-        <v>7204204</v>
+        <v>7204143</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,7 +5737,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210242</v>
+        <v>113210241</v>
       </c>
       <c r="B47" t="n">
         <v>78158</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543981</v>
+        <v>544013</v>
       </c>
       <c r="R47" t="n">
-        <v>7204228</v>
+        <v>7204204</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,7 +5849,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210254</v>
+        <v>113210242</v>
       </c>
       <c r="B48" t="n">
         <v>78158</v>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543828</v>
+        <v>543981</v>
       </c>
       <c r="R48" t="n">
-        <v>7204074</v>
+        <v>7204228</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210236</v>
+        <v>113210254</v>
       </c>
       <c r="B49" t="n">
-        <v>78240</v>
+        <v>78158</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5977,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544118</v>
+        <v>543828</v>
       </c>
       <c r="R49" t="n">
-        <v>7204143</v>
+        <v>7204074</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210278</v>
+        <v>113210241</v>
       </c>
       <c r="B2" t="n">
-        <v>81900</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543835</v>
+        <v>544013</v>
       </c>
       <c r="R2" t="n">
-        <v>7204068</v>
+        <v>7204204</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210214</v>
+        <v>113210236</v>
       </c>
       <c r="B3" t="n">
-        <v>79223</v>
+        <v>78240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543810</v>
+        <v>544118</v>
       </c>
       <c r="R3" t="n">
-        <v>7204198</v>
+        <v>7204143</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210217</v>
+        <v>113210214</v>
       </c>
       <c r="B4" t="n">
         <v>79223</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543841</v>
+        <v>543810</v>
       </c>
       <c r="R4" t="n">
-        <v>7204061</v>
+        <v>7204198</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210252</v>
+        <v>113210231</v>
       </c>
       <c r="B5" t="n">
-        <v>78158</v>
+        <v>79256</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543761</v>
+        <v>543836</v>
       </c>
       <c r="R5" t="n">
-        <v>7204153</v>
+        <v>7204058</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210231</v>
+        <v>113210238</v>
       </c>
       <c r="B6" t="n">
-        <v>79256</v>
+        <v>90101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543836</v>
+        <v>543860</v>
       </c>
       <c r="R6" t="n">
-        <v>7204058</v>
+        <v>7204033</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210238</v>
+        <v>113210244</v>
       </c>
       <c r="B7" t="n">
-        <v>90101</v>
+        <v>78158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543860</v>
+        <v>543984</v>
       </c>
       <c r="R7" t="n">
-        <v>7204033</v>
+        <v>7204170</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210208</v>
+        <v>113210217</v>
       </c>
       <c r="B8" t="n">
         <v>79223</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543983</v>
+        <v>543841</v>
       </c>
       <c r="R8" t="n">
-        <v>7204228</v>
+        <v>7204061</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210256</v>
+        <v>113210278</v>
       </c>
       <c r="B9" t="n">
-        <v>78158</v>
+        <v>81900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
         <v>543835</v>
       </c>
       <c r="R9" t="n">
-        <v>7204062</v>
+        <v>7204068</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210255</v>
+        <v>113210246</v>
       </c>
       <c r="B10" t="n">
         <v>78158</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543833</v>
+        <v>543953</v>
       </c>
       <c r="R10" t="n">
-        <v>7204063</v>
+        <v>7204079</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210233</v>
+        <v>113210280</v>
       </c>
       <c r="B11" t="n">
-        <v>77139</v>
+        <v>86379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543835</v>
+        <v>543753</v>
       </c>
       <c r="R11" t="n">
-        <v>7204068</v>
+        <v>7204132</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210240</v>
+        <v>113210279</v>
       </c>
       <c r="B12" t="n">
-        <v>78158</v>
+        <v>81900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544111</v>
+        <v>543833</v>
       </c>
       <c r="R12" t="n">
-        <v>7204146</v>
+        <v>7204061</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210250</v>
+        <v>113210257</v>
       </c>
       <c r="B13" t="n">
         <v>78158</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543822</v>
+        <v>543860</v>
       </c>
       <c r="R13" t="n">
-        <v>7204196</v>
+        <v>7204033</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210281</v>
+        <v>113210215</v>
       </c>
       <c r="B14" t="n">
-        <v>79255</v>
+        <v>79223</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543834</v>
+        <v>543762</v>
       </c>
       <c r="R14" t="n">
-        <v>7204070</v>
+        <v>7204149</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210224</v>
+        <v>113210216</v>
       </c>
       <c r="B15" t="n">
-        <v>74344</v>
+        <v>79223</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543833</v>
+        <v>543825</v>
       </c>
       <c r="R15" t="n">
-        <v>7204069</v>
+        <v>7204074</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210202</v>
+        <v>113210235</v>
       </c>
       <c r="B16" t="n">
-        <v>56914</v>
+        <v>77515</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,42 +2255,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544006</v>
+        <v>543858</v>
       </c>
       <c r="R16" t="n">
-        <v>7204169</v>
+        <v>7204151</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210279</v>
+        <v>113210210</v>
       </c>
       <c r="B17" t="n">
-        <v>81900</v>
+        <v>79223</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543833</v>
+        <v>543984</v>
       </c>
       <c r="R17" t="n">
-        <v>7204061</v>
+        <v>7204167</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210212</v>
+        <v>113210256</v>
       </c>
       <c r="B18" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543892</v>
+        <v>543835</v>
       </c>
       <c r="R18" t="n">
-        <v>7204108</v>
+        <v>7204062</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210184</v>
+        <v>113210251</v>
       </c>
       <c r="B19" t="n">
-        <v>77153</v>
+        <v>78158</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543833</v>
+        <v>543809</v>
       </c>
       <c r="R19" t="n">
-        <v>7204064</v>
+        <v>7204195</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2807,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210185</v>
+        <v>113210207</v>
       </c>
       <c r="B21" t="n">
-        <v>74339</v>
+        <v>79223</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543833</v>
+        <v>544012</v>
       </c>
       <c r="R21" t="n">
-        <v>7204064</v>
+        <v>7204204</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210191</v>
+        <v>113210228</v>
       </c>
       <c r="B22" t="n">
-        <v>56769</v>
+        <v>79222</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,43 +2931,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543999</v>
+        <v>544004</v>
       </c>
       <c r="R22" t="n">
-        <v>7204066</v>
+        <v>7204167</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210204</v>
+        <v>113210226</v>
       </c>
       <c r="B23" t="n">
-        <v>57366</v>
+        <v>79222</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,47 +3039,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543834</v>
+        <v>544013</v>
       </c>
       <c r="R23" t="n">
-        <v>7204061</v>
+        <v>7204205</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3124,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3134,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210280</v>
+        <v>113210204</v>
       </c>
       <c r="B24" t="n">
-        <v>86379</v>
+        <v>57366</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3173,38 +3151,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>102125</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543753</v>
+        <v>543834</v>
       </c>
       <c r="R24" t="n">
-        <v>7204132</v>
+        <v>7204061</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3236,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3246,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210248</v>
+        <v>113210208</v>
       </c>
       <c r="B25" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3313,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543892</v>
+        <v>543983</v>
       </c>
       <c r="R25" t="n">
-        <v>7204111</v>
+        <v>7204228</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3348,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3358,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3385,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210249</v>
+        <v>113210209</v>
       </c>
       <c r="B26" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3401,21 +3388,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3425,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543857</v>
+        <v>543983</v>
       </c>
       <c r="R26" t="n">
-        <v>7204152</v>
+        <v>7204203</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3460,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3470,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3609,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210213</v>
+        <v>113210205</v>
       </c>
       <c r="B28" t="n">
-        <v>79223</v>
+        <v>79249</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3621,25 +3608,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3649,10 +3636,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543821</v>
+        <v>543834</v>
       </c>
       <c r="R28" t="n">
-        <v>7204193</v>
+        <v>7204061</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3684,7 +3671,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3681,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,7 +3708,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210243</v>
+        <v>113210242</v>
       </c>
       <c r="B29" t="n">
         <v>78158</v>
@@ -3761,10 +3748,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543980</v>
+        <v>543981</v>
       </c>
       <c r="R29" t="n">
-        <v>7204203</v>
+        <v>7204228</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3796,7 +3783,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3793,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,10 +3820,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210216</v>
+        <v>113210243</v>
       </c>
       <c r="B30" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3849,21 +3836,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3873,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543825</v>
+        <v>543980</v>
       </c>
       <c r="R30" t="n">
-        <v>7204074</v>
+        <v>7204203</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3908,7 +3895,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,7 +3905,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210207</v>
+        <v>113210248</v>
       </c>
       <c r="B31" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3961,21 +3948,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3985,10 +3972,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544012</v>
+        <v>543892</v>
       </c>
       <c r="R31" t="n">
-        <v>7204204</v>
+        <v>7204111</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4020,7 +4007,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,7 +4017,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,7 +4044,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210209</v>
+        <v>113210212</v>
       </c>
       <c r="B32" t="n">
         <v>79223</v>
@@ -4097,10 +4084,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543983</v>
+        <v>543892</v>
       </c>
       <c r="R32" t="n">
-        <v>7204203</v>
+        <v>7204108</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4132,7 +4119,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4142,7 +4129,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210228</v>
+        <v>113210254</v>
       </c>
       <c r="B33" t="n">
-        <v>79222</v>
+        <v>78158</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4185,21 +4172,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4209,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544004</v>
+        <v>543828</v>
       </c>
       <c r="R33" t="n">
-        <v>7204167</v>
+        <v>7204074</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4244,7 +4231,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4254,7 +4241,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,7 +4268,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210245</v>
+        <v>113210255</v>
       </c>
       <c r="B34" t="n">
         <v>78158</v>
@@ -4321,10 +4308,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544004</v>
+        <v>543833</v>
       </c>
       <c r="R34" t="n">
-        <v>7204167</v>
+        <v>7204063</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4356,7 +4343,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4366,7 +4353,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,7 +4380,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210251</v>
+        <v>113210245</v>
       </c>
       <c r="B35" t="n">
         <v>78158</v>
@@ -4433,10 +4420,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543809</v>
+        <v>544004</v>
       </c>
       <c r="R35" t="n">
-        <v>7204195</v>
+        <v>7204167</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4468,7 +4455,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,7 +4465,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4505,7 +4492,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210244</v>
+        <v>113210240</v>
       </c>
       <c r="B36" t="n">
         <v>78158</v>
@@ -4545,10 +4532,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543984</v>
+        <v>544111</v>
       </c>
       <c r="R36" t="n">
-        <v>7204170</v>
+        <v>7204146</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4580,7 +4567,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4590,7 +4577,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210257</v>
+        <v>113210281</v>
       </c>
       <c r="B37" t="n">
-        <v>78158</v>
+        <v>79255</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4629,20 +4616,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4657,10 +4644,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543860</v>
+        <v>543834</v>
       </c>
       <c r="R37" t="n">
-        <v>7204033</v>
+        <v>7204070</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4692,7 +4679,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4702,7 +4689,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,10 +4716,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210253</v>
+        <v>113210184</v>
       </c>
       <c r="B38" t="n">
-        <v>78158</v>
+        <v>77153</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4745,21 +4732,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4769,10 +4756,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543753</v>
+        <v>543833</v>
       </c>
       <c r="R38" t="n">
-        <v>7204127</v>
+        <v>7204064</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4804,7 +4791,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,7 +4801,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4828,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210230</v>
+        <v>113210224</v>
       </c>
       <c r="B39" t="n">
-        <v>79256</v>
+        <v>74344</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,25 +4840,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4881,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543826</v>
+        <v>543833</v>
       </c>
       <c r="R39" t="n">
-        <v>7204074</v>
+        <v>7204069</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4916,7 +4903,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4926,7 +4913,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4953,10 +4940,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210205</v>
+        <v>113210185</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>74339</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4965,25 +4952,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4993,10 +4980,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543834</v>
+        <v>543833</v>
       </c>
       <c r="R40" t="n">
-        <v>7204061</v>
+        <v>7204064</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5028,7 +5015,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5038,7 +5025,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5065,10 +5052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210235</v>
+        <v>113210213</v>
       </c>
       <c r="B41" t="n">
-        <v>77515</v>
+        <v>79223</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5077,25 +5064,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5105,10 +5092,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543858</v>
+        <v>543821</v>
       </c>
       <c r="R41" t="n">
-        <v>7204151</v>
+        <v>7204193</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5140,7 +5127,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5150,7 +5137,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5177,10 +5164,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210226</v>
+        <v>113210230</v>
       </c>
       <c r="B42" t="n">
-        <v>79222</v>
+        <v>79256</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5189,25 +5176,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5217,10 +5204,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544013</v>
+        <v>543826</v>
       </c>
       <c r="R42" t="n">
-        <v>7204205</v>
+        <v>7204074</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5252,7 +5239,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5249,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5289,10 +5276,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210210</v>
+        <v>113210250</v>
       </c>
       <c r="B43" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5305,21 +5292,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5329,10 +5316,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543984</v>
+        <v>543822</v>
       </c>
       <c r="R43" t="n">
-        <v>7204167</v>
+        <v>7204196</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5364,7 +5351,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5374,7 +5361,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5401,10 +5388,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210246</v>
+        <v>113210233</v>
       </c>
       <c r="B44" t="n">
-        <v>78158</v>
+        <v>77139</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5417,21 +5404,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5441,10 +5428,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543953</v>
+        <v>543835</v>
       </c>
       <c r="R44" t="n">
-        <v>7204079</v>
+        <v>7204068</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5476,7 +5463,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5486,7 +5473,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5513,10 +5500,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210215</v>
+        <v>113210253</v>
       </c>
       <c r="B45" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5529,21 +5516,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5553,10 +5540,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543762</v>
+        <v>543753</v>
       </c>
       <c r="R45" t="n">
-        <v>7204149</v>
+        <v>7204127</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5588,7 +5575,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5598,7 +5585,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5625,10 +5612,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210236</v>
+        <v>113210252</v>
       </c>
       <c r="B46" t="n">
-        <v>78240</v>
+        <v>78158</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5641,21 +5628,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5665,10 +5652,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544118</v>
+        <v>543761</v>
       </c>
       <c r="R46" t="n">
-        <v>7204143</v>
+        <v>7204153</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5687,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5697,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5724,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210241</v>
+        <v>113210191</v>
       </c>
       <c r="B47" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5753,34 +5740,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544013</v>
+        <v>543999</v>
       </c>
       <c r="R47" t="n">
-        <v>7204204</v>
+        <v>7204066</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5808,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5818,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5845,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210242</v>
+        <v>113210227</v>
       </c>
       <c r="B48" t="n">
-        <v>78158</v>
+        <v>79222</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5865,21 +5861,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,7 +5885,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543981</v>
+        <v>543983</v>
       </c>
       <c r="R48" t="n">
         <v>7204228</v>
@@ -5961,7 +5957,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210254</v>
+        <v>113210249</v>
       </c>
       <c r="B49" t="n">
         <v>78158</v>
@@ -6001,10 +5997,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543828</v>
+        <v>543857</v>
       </c>
       <c r="R49" t="n">
-        <v>7204074</v>
+        <v>7204152</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6032,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6042,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6069,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210227</v>
+        <v>113210202</v>
       </c>
       <c r="B50" t="n">
-        <v>79222</v>
+        <v>56914</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,34 +6085,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543983</v>
+        <v>544006</v>
       </c>
       <c r="R50" t="n">
-        <v>7204228</v>
+        <v>7204169</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210241</v>
+        <v>113210204</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544013</v>
+        <v>543834</v>
       </c>
       <c r="R2" t="n">
-        <v>7204204</v>
+        <v>7204061</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210236</v>
+        <v>113210254</v>
       </c>
       <c r="B3" t="n">
-        <v>78240</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544118</v>
+        <v>543828</v>
       </c>
       <c r="R3" t="n">
-        <v>7204143</v>
+        <v>7204074</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210214</v>
+        <v>113210227</v>
       </c>
       <c r="B4" t="n">
-        <v>79223</v>
+        <v>79228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543810</v>
+        <v>543983</v>
       </c>
       <c r="R4" t="n">
-        <v>7204198</v>
+        <v>7204228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210231</v>
+        <v>113210213</v>
       </c>
       <c r="B5" t="n">
-        <v>79256</v>
+        <v>79229</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543836</v>
+        <v>543821</v>
       </c>
       <c r="R5" t="n">
-        <v>7204058</v>
+        <v>7204193</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210238</v>
+        <v>113210256</v>
       </c>
       <c r="B6" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543860</v>
+        <v>543835</v>
       </c>
       <c r="R6" t="n">
-        <v>7204033</v>
+        <v>7204062</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210244</v>
+        <v>113210257</v>
       </c>
       <c r="B7" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543984</v>
+        <v>543860</v>
       </c>
       <c r="R7" t="n">
-        <v>7204170</v>
+        <v>7204033</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210217</v>
+        <v>113210253</v>
       </c>
       <c r="B8" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543841</v>
+        <v>543753</v>
       </c>
       <c r="R8" t="n">
-        <v>7204061</v>
+        <v>7204127</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210278</v>
+        <v>113210216</v>
       </c>
       <c r="B9" t="n">
-        <v>81900</v>
+        <v>79229</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543835</v>
+        <v>543825</v>
       </c>
       <c r="R9" t="n">
-        <v>7204068</v>
+        <v>7204074</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210246</v>
+        <v>113210243</v>
       </c>
       <c r="B10" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543953</v>
+        <v>543980</v>
       </c>
       <c r="R10" t="n">
-        <v>7204079</v>
+        <v>7204203</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210280</v>
+        <v>113210278</v>
       </c>
       <c r="B11" t="n">
-        <v>86379</v>
+        <v>81906</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543753</v>
+        <v>543835</v>
       </c>
       <c r="R11" t="n">
-        <v>7204132</v>
+        <v>7204068</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210279</v>
+        <v>113210215</v>
       </c>
       <c r="B12" t="n">
-        <v>81900</v>
+        <v>79229</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543833</v>
+        <v>543762</v>
       </c>
       <c r="R12" t="n">
-        <v>7204061</v>
+        <v>7204149</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210257</v>
+        <v>113210210</v>
       </c>
       <c r="B13" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543860</v>
+        <v>543984</v>
       </c>
       <c r="R13" t="n">
-        <v>7204033</v>
+        <v>7204167</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210215</v>
+        <v>113210191</v>
       </c>
       <c r="B14" t="n">
-        <v>79223</v>
+        <v>56773</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,34 +2044,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543762</v>
+        <v>543999</v>
       </c>
       <c r="R14" t="n">
-        <v>7204149</v>
+        <v>7204066</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2112,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2122,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210216</v>
+        <v>113210252</v>
       </c>
       <c r="B15" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2165,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543825</v>
+        <v>543761</v>
       </c>
       <c r="R15" t="n">
-        <v>7204074</v>
+        <v>7204153</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2224,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2234,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2261,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210235</v>
+        <v>113210224</v>
       </c>
       <c r="B16" t="n">
-        <v>77515</v>
+        <v>74350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2273,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>498</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2301,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543858</v>
+        <v>543833</v>
       </c>
       <c r="R16" t="n">
-        <v>7204151</v>
+        <v>7204069</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2336,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2346,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210210</v>
+        <v>113210207</v>
       </c>
       <c r="B17" t="n">
-        <v>79223</v>
+        <v>79229</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543984</v>
+        <v>544012</v>
       </c>
       <c r="R17" t="n">
-        <v>7204167</v>
+        <v>7204204</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2485,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210256</v>
+        <v>113210228</v>
       </c>
       <c r="B18" t="n">
-        <v>78158</v>
+        <v>79228</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2501,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543835</v>
+        <v>544004</v>
       </c>
       <c r="R18" t="n">
-        <v>7204062</v>
+        <v>7204167</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210251</v>
+        <v>113210226</v>
       </c>
       <c r="B19" t="n">
-        <v>78158</v>
+        <v>79228</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2613,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543809</v>
+        <v>544013</v>
       </c>
       <c r="R19" t="n">
-        <v>7204195</v>
+        <v>7204205</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2672,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2682,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2709,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210189</v>
+        <v>113210246</v>
       </c>
       <c r="B20" t="n">
-        <v>90083</v>
+        <v>78164</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2725,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543860</v>
+        <v>543953</v>
       </c>
       <c r="R20" t="n">
-        <v>7204034</v>
+        <v>7204079</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2784,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2794,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2821,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210207</v>
+        <v>113210236</v>
       </c>
       <c r="B21" t="n">
-        <v>79223</v>
+        <v>78246</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2837,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2861,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544012</v>
+        <v>544118</v>
       </c>
       <c r="R21" t="n">
-        <v>7204204</v>
+        <v>7204143</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2896,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2906,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2933,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210228</v>
+        <v>113210238</v>
       </c>
       <c r="B22" t="n">
-        <v>79222</v>
+        <v>90107</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2949,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2973,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544004</v>
+        <v>543860</v>
       </c>
       <c r="R22" t="n">
-        <v>7204167</v>
+        <v>7204033</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +3008,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3018,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210226</v>
+        <v>113210279</v>
       </c>
       <c r="B23" t="n">
-        <v>79222</v>
+        <v>81906</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3061,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3085,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544013</v>
+        <v>543833</v>
       </c>
       <c r="R23" t="n">
-        <v>7204205</v>
+        <v>7204061</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,7 +3120,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3130,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3157,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210204</v>
+        <v>113210242</v>
       </c>
       <c r="B24" t="n">
-        <v>57366</v>
+        <v>78164</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,47 +3169,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543834</v>
+        <v>543981</v>
       </c>
       <c r="R24" t="n">
-        <v>7204061</v>
+        <v>7204228</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3232,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3242,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210208</v>
+        <v>113210233</v>
       </c>
       <c r="B25" t="n">
-        <v>79223</v>
+        <v>77145</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3276,21 +3285,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543983</v>
+        <v>543835</v>
       </c>
       <c r="R25" t="n">
-        <v>7204228</v>
+        <v>7204068</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3344,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3354,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3381,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210209</v>
+        <v>113210280</v>
       </c>
       <c r="B26" t="n">
-        <v>79223</v>
+        <v>86385</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3388,21 +3397,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3421,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543983</v>
+        <v>543753</v>
       </c>
       <c r="R26" t="n">
-        <v>7204203</v>
+        <v>7204132</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3447,7 +3456,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3466,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210211</v>
+        <v>113210202</v>
       </c>
       <c r="B27" t="n">
-        <v>79223</v>
+        <v>56918</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,34 +3509,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544004</v>
+        <v>544006</v>
       </c>
       <c r="R27" t="n">
-        <v>7204168</v>
+        <v>7204169</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3596,10 +3609,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210205</v>
+        <v>113210217</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79229</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,25 +3621,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3636,7 +3649,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543834</v>
+        <v>543841</v>
       </c>
       <c r="R28" t="n">
         <v>7204061</v>
@@ -3671,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3681,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210242</v>
+        <v>113210212</v>
       </c>
       <c r="B29" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3724,21 +3737,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3748,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543981</v>
+        <v>543892</v>
       </c>
       <c r="R29" t="n">
-        <v>7204228</v>
+        <v>7204108</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3783,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3793,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3820,10 +3833,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210243</v>
+        <v>113210249</v>
       </c>
       <c r="B30" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3860,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543980</v>
+        <v>543857</v>
       </c>
       <c r="R30" t="n">
-        <v>7204203</v>
+        <v>7204152</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3895,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3905,7 +3918,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,10 +3945,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210248</v>
+        <v>113210230</v>
       </c>
       <c r="B31" t="n">
-        <v>78158</v>
+        <v>79262</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,25 +3957,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3972,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543892</v>
+        <v>543826</v>
       </c>
       <c r="R31" t="n">
-        <v>7204111</v>
+        <v>7204074</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4007,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4017,7 +4030,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210212</v>
+        <v>113210250</v>
       </c>
       <c r="B32" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4060,21 +4073,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4084,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543892</v>
+        <v>543822</v>
       </c>
       <c r="R32" t="n">
-        <v>7204108</v>
+        <v>7204196</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4119,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4129,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,10 +4169,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210254</v>
+        <v>113210245</v>
       </c>
       <c r="B33" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4196,10 +4209,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543828</v>
+        <v>544004</v>
       </c>
       <c r="R33" t="n">
-        <v>7204074</v>
+        <v>7204167</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4231,7 +4244,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4241,7 +4254,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4268,10 +4281,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210255</v>
+        <v>113210189</v>
       </c>
       <c r="B34" t="n">
-        <v>78158</v>
+        <v>90089</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,21 +4297,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4308,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543833</v>
+        <v>543860</v>
       </c>
       <c r="R34" t="n">
-        <v>7204063</v>
+        <v>7204034</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4343,7 +4356,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4353,7 +4366,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,10 +4393,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210245</v>
+        <v>113210244</v>
       </c>
       <c r="B35" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4420,10 +4433,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544004</v>
+        <v>543984</v>
       </c>
       <c r="R35" t="n">
-        <v>7204167</v>
+        <v>7204170</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4455,7 +4468,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4465,7 +4478,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,10 +4505,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210240</v>
+        <v>113210248</v>
       </c>
       <c r="B36" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,10 +4545,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544111</v>
+        <v>543892</v>
       </c>
       <c r="R36" t="n">
-        <v>7204146</v>
+        <v>7204111</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4567,7 +4580,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4577,7 +4590,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210281</v>
+        <v>113210241</v>
       </c>
       <c r="B37" t="n">
-        <v>79255</v>
+        <v>78164</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4616,20 +4629,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4644,10 +4657,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543834</v>
+        <v>544013</v>
       </c>
       <c r="R37" t="n">
-        <v>7204070</v>
+        <v>7204204</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4679,7 +4692,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4689,7 +4702,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4716,10 +4729,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210184</v>
+        <v>113210251</v>
       </c>
       <c r="B38" t="n">
-        <v>77153</v>
+        <v>78164</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4732,21 +4745,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4756,10 +4769,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543833</v>
+        <v>543809</v>
       </c>
       <c r="R38" t="n">
-        <v>7204064</v>
+        <v>7204195</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4791,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4801,7 +4814,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210224</v>
+        <v>113210205</v>
       </c>
       <c r="B39" t="n">
-        <v>74344</v>
+        <v>79255</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4840,25 +4853,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4868,10 +4881,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543833</v>
+        <v>543834</v>
       </c>
       <c r="R39" t="n">
-        <v>7204069</v>
+        <v>7204061</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4903,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4913,7 +4926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4940,10 +4953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210185</v>
+        <v>113210209</v>
       </c>
       <c r="B40" t="n">
-        <v>74339</v>
+        <v>79229</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4956,21 +4969,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4980,10 +4993,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543833</v>
+        <v>543983</v>
       </c>
       <c r="R40" t="n">
-        <v>7204064</v>
+        <v>7204203</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5015,7 +5028,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5025,7 +5038,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5052,10 +5065,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210213</v>
+        <v>113210211</v>
       </c>
       <c r="B41" t="n">
-        <v>79223</v>
+        <v>79229</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5092,10 +5105,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543821</v>
+        <v>544004</v>
       </c>
       <c r="R41" t="n">
-        <v>7204193</v>
+        <v>7204168</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5127,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5137,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5164,10 +5177,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210230</v>
+        <v>113210214</v>
       </c>
       <c r="B42" t="n">
-        <v>79256</v>
+        <v>79229</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5176,25 +5189,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5204,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543826</v>
+        <v>543810</v>
       </c>
       <c r="R42" t="n">
-        <v>7204074</v>
+        <v>7204198</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5239,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5249,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210250</v>
+        <v>113210281</v>
       </c>
       <c r="B43" t="n">
-        <v>78158</v>
+        <v>79261</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5288,20 +5301,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5316,10 +5329,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543822</v>
+        <v>543834</v>
       </c>
       <c r="R43" t="n">
-        <v>7204196</v>
+        <v>7204070</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5351,7 +5364,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5361,7 +5374,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,10 +5401,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210233</v>
+        <v>113210208</v>
       </c>
       <c r="B44" t="n">
-        <v>77139</v>
+        <v>79229</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5404,21 +5417,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5428,10 +5441,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543835</v>
+        <v>543983</v>
       </c>
       <c r="R44" t="n">
-        <v>7204068</v>
+        <v>7204228</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5463,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5473,7 +5486,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5500,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210253</v>
+        <v>113210235</v>
       </c>
       <c r="B45" t="n">
-        <v>78158</v>
+        <v>77521</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5512,25 +5525,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5540,10 +5553,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543753</v>
+        <v>543858</v>
       </c>
       <c r="R45" t="n">
-        <v>7204127</v>
+        <v>7204151</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5575,7 +5588,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5585,7 +5598,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210252</v>
+        <v>113210240</v>
       </c>
       <c r="B46" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5652,10 +5665,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543761</v>
+        <v>544111</v>
       </c>
       <c r="R46" t="n">
-        <v>7204153</v>
+        <v>7204146</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5687,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5697,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5724,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210191</v>
+        <v>113210184</v>
       </c>
       <c r="B47" t="n">
-        <v>56769</v>
+        <v>77159</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5740,43 +5753,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543999</v>
+        <v>543833</v>
       </c>
       <c r="R47" t="n">
-        <v>7204066</v>
+        <v>7204064</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5808,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5818,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5845,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210227</v>
+        <v>113210231</v>
       </c>
       <c r="B48" t="n">
-        <v>79222</v>
+        <v>79262</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5857,25 +5861,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5885,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543983</v>
+        <v>543836</v>
       </c>
       <c r="R48" t="n">
-        <v>7204228</v>
+        <v>7204058</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5920,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5930,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5957,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210249</v>
+        <v>113210185</v>
       </c>
       <c r="B49" t="n">
-        <v>78158</v>
+        <v>74345</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5973,21 +5977,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5997,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543857</v>
+        <v>543833</v>
       </c>
       <c r="R49" t="n">
-        <v>7204152</v>
+        <v>7204064</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6032,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6042,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6069,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210202</v>
+        <v>113210255</v>
       </c>
       <c r="B50" t="n">
-        <v>56914</v>
+        <v>78164</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6085,38 +6089,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544006</v>
+        <v>543833</v>
       </c>
       <c r="R50" t="n">
-        <v>7204169</v>
+        <v>7204063</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210204</v>
+        <v>113210224</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>74350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543834</v>
+        <v>543833</v>
       </c>
       <c r="R2" t="n">
-        <v>7204061</v>
+        <v>7204069</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210254</v>
+        <v>113210278</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>81906</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543828</v>
+        <v>543835</v>
       </c>
       <c r="R3" t="n">
-        <v>7204074</v>
+        <v>7204068</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210227</v>
+        <v>113210215</v>
       </c>
       <c r="B4" t="n">
-        <v>79228</v>
+        <v>79229</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543983</v>
+        <v>543762</v>
       </c>
       <c r="R4" t="n">
-        <v>7204228</v>
+        <v>7204149</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210213</v>
+        <v>113210251</v>
       </c>
       <c r="B5" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543821</v>
+        <v>543809</v>
       </c>
       <c r="R5" t="n">
-        <v>7204193</v>
+        <v>7204195</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210256</v>
+        <v>113210244</v>
       </c>
       <c r="B6" t="n">
         <v>78164</v>
@@ -1172,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543835</v>
+        <v>543984</v>
       </c>
       <c r="R6" t="n">
-        <v>7204062</v>
+        <v>7204170</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210257</v>
+        <v>113210185</v>
       </c>
       <c r="B7" t="n">
-        <v>78164</v>
+        <v>74345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543860</v>
+        <v>543833</v>
       </c>
       <c r="R7" t="n">
-        <v>7204033</v>
+        <v>7204064</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210253</v>
+        <v>113210242</v>
       </c>
       <c r="B8" t="n">
         <v>78164</v>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543753</v>
+        <v>543981</v>
       </c>
       <c r="R8" t="n">
-        <v>7204127</v>
+        <v>7204228</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210216</v>
+        <v>113210250</v>
       </c>
       <c r="B9" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543825</v>
+        <v>543822</v>
       </c>
       <c r="R9" t="n">
-        <v>7204074</v>
+        <v>7204196</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210243</v>
+        <v>113210280</v>
       </c>
       <c r="B10" t="n">
-        <v>78164</v>
+        <v>86385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543980</v>
+        <v>543753</v>
       </c>
       <c r="R10" t="n">
-        <v>7204203</v>
+        <v>7204132</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210278</v>
+        <v>113210191</v>
       </c>
       <c r="B11" t="n">
-        <v>81906</v>
+        <v>56773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,34 +1699,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543835</v>
+        <v>543999</v>
       </c>
       <c r="R11" t="n">
-        <v>7204068</v>
+        <v>7204066</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,7 +1804,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210215</v>
+        <v>113210217</v>
       </c>
       <c r="B12" t="n">
         <v>79229</v>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543762</v>
+        <v>543841</v>
       </c>
       <c r="R12" t="n">
-        <v>7204149</v>
+        <v>7204061</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210210</v>
+        <v>113210246</v>
       </c>
       <c r="B13" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543984</v>
+        <v>543953</v>
       </c>
       <c r="R13" t="n">
-        <v>7204167</v>
+        <v>7204079</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210191</v>
+        <v>113210227</v>
       </c>
       <c r="B14" t="n">
-        <v>56773</v>
+        <v>79228</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,43 +2044,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543999</v>
+        <v>543983</v>
       </c>
       <c r="R14" t="n">
-        <v>7204066</v>
+        <v>7204228</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2112,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2122,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210252</v>
+        <v>113210213</v>
       </c>
       <c r="B15" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2189,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543761</v>
+        <v>543821</v>
       </c>
       <c r="R15" t="n">
-        <v>7204153</v>
+        <v>7204193</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2224,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2234,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210224</v>
+        <v>113210226</v>
       </c>
       <c r="B16" t="n">
-        <v>74350</v>
+        <v>79228</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,21 +2268,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2301,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543833</v>
+        <v>544013</v>
       </c>
       <c r="R16" t="n">
-        <v>7204069</v>
+        <v>7204205</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2336,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2346,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210207</v>
+        <v>113210189</v>
       </c>
       <c r="B17" t="n">
-        <v>79229</v>
+        <v>90089</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,21 +2380,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2413,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544012</v>
+        <v>543860</v>
       </c>
       <c r="R17" t="n">
-        <v>7204204</v>
+        <v>7204034</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2448,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210228</v>
+        <v>113210254</v>
       </c>
       <c r="B18" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,21 +2492,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544004</v>
+        <v>543828</v>
       </c>
       <c r="R18" t="n">
-        <v>7204167</v>
+        <v>7204074</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2560,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210226</v>
+        <v>113210253</v>
       </c>
       <c r="B19" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2613,21 +2604,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2637,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544013</v>
+        <v>543753</v>
       </c>
       <c r="R19" t="n">
-        <v>7204205</v>
+        <v>7204127</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2672,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2682,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210246</v>
+        <v>113210202</v>
       </c>
       <c r="B20" t="n">
-        <v>78164</v>
+        <v>56918</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2725,34 +2716,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543953</v>
+        <v>544006</v>
       </c>
       <c r="R20" t="n">
-        <v>7204079</v>
+        <v>7204169</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2784,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2794,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2821,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210236</v>
+        <v>113210210</v>
       </c>
       <c r="B21" t="n">
-        <v>78246</v>
+        <v>79229</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2837,21 +2832,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2861,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544118</v>
+        <v>543984</v>
       </c>
       <c r="R21" t="n">
-        <v>7204143</v>
+        <v>7204167</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2896,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2906,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210238</v>
+        <v>113210211</v>
       </c>
       <c r="B22" t="n">
-        <v>90107</v>
+        <v>79229</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2949,21 +2944,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2973,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543860</v>
+        <v>544004</v>
       </c>
       <c r="R22" t="n">
-        <v>7204033</v>
+        <v>7204168</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3008,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3018,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210279</v>
+        <v>113210252</v>
       </c>
       <c r="B23" t="n">
-        <v>81906</v>
+        <v>78164</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3061,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543833</v>
+        <v>543761</v>
       </c>
       <c r="R23" t="n">
-        <v>7204061</v>
+        <v>7204153</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3120,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3130,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3157,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210242</v>
+        <v>113210236</v>
       </c>
       <c r="B24" t="n">
-        <v>78164</v>
+        <v>78246</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3173,21 +3168,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543981</v>
+        <v>544118</v>
       </c>
       <c r="R24" t="n">
-        <v>7204228</v>
+        <v>7204143</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3232,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3242,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3269,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210233</v>
+        <v>113210248</v>
       </c>
       <c r="B25" t="n">
-        <v>77145</v>
+        <v>78164</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,21 +3280,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3309,10 +3304,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543835</v>
+        <v>543892</v>
       </c>
       <c r="R25" t="n">
-        <v>7204068</v>
+        <v>7204111</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3344,7 +3339,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3349,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,10 +3376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210280</v>
+        <v>113210233</v>
       </c>
       <c r="B26" t="n">
-        <v>86385</v>
+        <v>77145</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3397,21 +3392,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543753</v>
+        <v>543835</v>
       </c>
       <c r="R26" t="n">
-        <v>7204132</v>
+        <v>7204068</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3456,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3466,7 +3461,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3493,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210202</v>
+        <v>113210238</v>
       </c>
       <c r="B27" t="n">
-        <v>56918</v>
+        <v>90107</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3509,38 +3504,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544006</v>
+        <v>543860</v>
       </c>
       <c r="R27" t="n">
-        <v>7204169</v>
+        <v>7204033</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3572,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3582,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,7 +3600,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210217</v>
+        <v>113210208</v>
       </c>
       <c r="B28" t="n">
         <v>79229</v>
@@ -3649,10 +3640,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543841</v>
+        <v>543983</v>
       </c>
       <c r="R28" t="n">
-        <v>7204061</v>
+        <v>7204228</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3684,7 +3675,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3685,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3721,10 +3712,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210212</v>
+        <v>113210245</v>
       </c>
       <c r="B29" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,21 +3728,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543892</v>
+        <v>544004</v>
       </c>
       <c r="R29" t="n">
-        <v>7204108</v>
+        <v>7204167</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3796,7 +3787,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3797,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,10 +3824,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210249</v>
+        <v>113210228</v>
       </c>
       <c r="B30" t="n">
-        <v>78164</v>
+        <v>79228</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3849,21 +3840,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3873,10 +3864,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543857</v>
+        <v>544004</v>
       </c>
       <c r="R30" t="n">
-        <v>7204152</v>
+        <v>7204167</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3908,7 +3899,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3918,7 +3909,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3945,10 +3936,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210230</v>
+        <v>113210184</v>
       </c>
       <c r="B31" t="n">
-        <v>79262</v>
+        <v>77159</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3957,25 +3948,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3985,10 +3976,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543826</v>
+        <v>543833</v>
       </c>
       <c r="R31" t="n">
-        <v>7204074</v>
+        <v>7204064</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4020,7 +4011,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4030,7 +4021,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,7 +4048,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210250</v>
+        <v>113210249</v>
       </c>
       <c r="B32" t="n">
         <v>78164</v>
@@ -4097,10 +4088,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543822</v>
+        <v>543857</v>
       </c>
       <c r="R32" t="n">
-        <v>7204196</v>
+        <v>7204152</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4132,7 +4123,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4142,7 +4133,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,10 +4160,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210245</v>
+        <v>113210230</v>
       </c>
       <c r="B33" t="n">
-        <v>78164</v>
+        <v>79262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,25 +4172,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4209,10 +4200,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544004</v>
+        <v>543826</v>
       </c>
       <c r="R33" t="n">
-        <v>7204167</v>
+        <v>7204074</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4244,7 +4235,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4254,7 +4245,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210189</v>
+        <v>113210255</v>
       </c>
       <c r="B34" t="n">
-        <v>90089</v>
+        <v>78164</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4297,21 +4288,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4321,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543860</v>
+        <v>543833</v>
       </c>
       <c r="R34" t="n">
-        <v>7204034</v>
+        <v>7204063</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4356,7 +4347,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4366,7 +4357,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,10 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210244</v>
+        <v>113210281</v>
       </c>
       <c r="B35" t="n">
-        <v>78164</v>
+        <v>79261</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4405,20 +4396,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4433,10 +4424,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543984</v>
+        <v>543834</v>
       </c>
       <c r="R35" t="n">
-        <v>7204170</v>
+        <v>7204070</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4468,7 +4459,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,7 +4469,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4505,7 +4496,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210248</v>
+        <v>113210241</v>
       </c>
       <c r="B36" t="n">
         <v>78164</v>
@@ -4545,10 +4536,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543892</v>
+        <v>544013</v>
       </c>
       <c r="R36" t="n">
-        <v>7204111</v>
+        <v>7204204</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4580,7 +4571,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4590,7 +4581,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,7 +4608,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210241</v>
+        <v>113210256</v>
       </c>
       <c r="B37" t="n">
         <v>78164</v>
@@ -4657,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544013</v>
+        <v>543835</v>
       </c>
       <c r="R37" t="n">
-        <v>7204204</v>
+        <v>7204062</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4692,7 +4683,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4702,7 +4693,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210251</v>
+        <v>113210205</v>
       </c>
       <c r="B38" t="n">
-        <v>78164</v>
+        <v>79255</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4741,25 +4732,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4769,10 +4760,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543809</v>
+        <v>543834</v>
       </c>
       <c r="R38" t="n">
-        <v>7204195</v>
+        <v>7204061</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4804,7 +4795,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,7 +4805,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4832,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210205</v>
+        <v>113210243</v>
       </c>
       <c r="B39" t="n">
-        <v>79255</v>
+        <v>78164</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,25 +4844,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4881,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543834</v>
+        <v>543980</v>
       </c>
       <c r="R39" t="n">
-        <v>7204061</v>
+        <v>7204203</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4916,7 +4907,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4926,7 +4917,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4953,7 +4944,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113210209</v>
+        <v>113210207</v>
       </c>
       <c r="B40" t="n">
         <v>79229</v>
@@ -4993,10 +4984,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543983</v>
+        <v>544012</v>
       </c>
       <c r="R40" t="n">
-        <v>7204203</v>
+        <v>7204204</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5028,7 +5019,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5038,7 +5029,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5065,10 +5056,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113210211</v>
+        <v>113210204</v>
       </c>
       <c r="B41" t="n">
-        <v>79229</v>
+        <v>57370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5077,38 +5068,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>102125</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544004</v>
+        <v>543834</v>
       </c>
       <c r="R41" t="n">
-        <v>7204168</v>
+        <v>7204061</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5177,7 +5177,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113210214</v>
+        <v>113210209</v>
       </c>
       <c r="B42" t="n">
         <v>79229</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543810</v>
+        <v>543983</v>
       </c>
       <c r="R42" t="n">
-        <v>7204198</v>
+        <v>7204203</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113210281</v>
+        <v>113210279</v>
       </c>
       <c r="B43" t="n">
-        <v>79261</v>
+        <v>81906</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5301,25 +5301,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543834</v>
+        <v>543833</v>
       </c>
       <c r="R43" t="n">
-        <v>7204070</v>
+        <v>7204061</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5401,10 +5401,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113210208</v>
+        <v>113210240</v>
       </c>
       <c r="B44" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5417,21 +5417,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543983</v>
+        <v>544111</v>
       </c>
       <c r="R44" t="n">
-        <v>7204228</v>
+        <v>7204146</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5513,10 +5513,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113210235</v>
+        <v>113210212</v>
       </c>
       <c r="B45" t="n">
-        <v>77521</v>
+        <v>79229</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543858</v>
+        <v>543892</v>
       </c>
       <c r="R45" t="n">
-        <v>7204151</v>
+        <v>7204108</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113210240</v>
+        <v>113210214</v>
       </c>
       <c r="B46" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544111</v>
+        <v>543810</v>
       </c>
       <c r="R46" t="n">
-        <v>7204146</v>
+        <v>7204198</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113210184</v>
+        <v>113210257</v>
       </c>
       <c r="B47" t="n">
-        <v>77159</v>
+        <v>78164</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5753,21 +5753,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543833</v>
+        <v>543860</v>
       </c>
       <c r="R47" t="n">
-        <v>7204064</v>
+        <v>7204033</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,10 +5849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113210231</v>
+        <v>113210235</v>
       </c>
       <c r="B48" t="n">
-        <v>79262</v>
+        <v>77521</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5861,25 +5861,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543836</v>
+        <v>543858</v>
       </c>
       <c r="R48" t="n">
-        <v>7204058</v>
+        <v>7204151</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5961,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113210185</v>
+        <v>113210231</v>
       </c>
       <c r="B49" t="n">
-        <v>74345</v>
+        <v>79262</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5973,25 +5973,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543833</v>
+        <v>543836</v>
       </c>
       <c r="R49" t="n">
-        <v>7204064</v>
+        <v>7204058</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6073,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113210255</v>
+        <v>113210216</v>
       </c>
       <c r="B50" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543833</v>
+        <v>543825</v>
       </c>
       <c r="R50" t="n">
-        <v>7204063</v>
+        <v>7204074</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 48190-2023 artfynd.xlsx
+++ b/artfynd/A 48190-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
